--- a/ACQL Dashboard.xlsx
+++ b/ACQL Dashboard.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sam52\OneDrive\Documents\Code x\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{06256E13-2F93-44AB-B58C-F65081626BD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{1532C6A4-56D7-4287-AED0-A52BCDCDEF5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1792" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1791" uniqueCount="256">
   <si>
     <t>Week 2</t>
   </si>
@@ -770,9 +770,6 @@
     <t xml:space="preserve"> seattle</t>
   </si>
   <si>
-    <t xml:space="preserve"> KANSAS CITY </t>
-  </si>
-  <si>
     <t xml:space="preserve"> LOS ANGELES RAMS </t>
   </si>
   <si>
@@ -794,9 +791,6 @@
     <t xml:space="preserve"> indianapolis</t>
   </si>
   <si>
-    <t xml:space="preserve"> new york giants</t>
-  </si>
-  <si>
     <t xml:space="preserve"> SAN FRANCISCO </t>
   </si>
   <si>
@@ -816,6 +810,24 @@
   </si>
   <si>
     <t>🏈 WEEK 3 — ACQL</t>
+  </si>
+  <si>
+    <t>(GB by 7)</t>
+  </si>
+  <si>
+    <t>(Det by 7)</t>
+  </si>
+  <si>
+    <t>(KC by 12)</t>
+  </si>
+  <si>
+    <t>(Sea by 8)</t>
+  </si>
+  <si>
+    <t>(SF by 9)</t>
+  </si>
+  <si>
+    <t>(Buf by 8)</t>
   </si>
 </sst>
 </file>
@@ -3537,15 +3549,15 @@
       <c r="J5" s="45"/>
       <c r="K5" s="47">
         <f ca="1">_xlfn.XLOOKUP(I5,Season!A5:A39,Season!V5:V39)</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L5" s="47">
         <f ca="1">AVERAGE(_xlfn.XLOOKUP(I5,Season!A5:A39,Season!V5:V39))</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M5" s="50">
         <f ca="1">_xlfn.XLOOKUP(I5,Winnings!A5:A39,Winnings!U5:U39)</f>
-        <v>110</v>
+        <v>35.5</v>
       </c>
       <c r="O5" s="16"/>
       <c r="P5" s="45"/>
@@ -3613,15 +3625,15 @@
       </c>
       <c r="C7" s="21">
         <f t="array" aca="1" ref="C7" ca="1">IF(B7="","",INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B7)))</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D7" s="21">
         <f t="array" aca="1" ref="D7" ca="1">IF(B7="","",INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$C$10:$C$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B7)))</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E7" s="23">
         <f t="shared" ref="E7:E41" ca="1" si="0">IF(B7="","",D7/16)</f>
-        <v>0.8125</v>
+        <v>0.75</v>
       </c>
       <c r="F7" s="21">
         <f t="shared" ref="F7:F41" ca="1" si="1">$C$7-C7</f>
@@ -3657,11 +3669,11 @@
       </c>
       <c r="R7" s="21">
         <f t="array" aca="1" ref="R7" ca="1">_xlfn.XLOOKUP(Q7,Table2[Player],Season!$T$5:$T$39)</f>
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="S7" s="23">
         <f ca="1">IFERROR(SUM(_xlfn.XLOOKUP(Q7,Table2[Player],Table2[Season Wins]))/SUM(Season!$B$3:$S$3),0)</f>
-        <v>0.10294117647058823</v>
+        <v>9.9264705882352935E-2</v>
       </c>
       <c r="T7" s="21">
         <f t="shared" ref="T7:T41" ca="1" si="3">$R$7-R7</f>
@@ -3669,7 +3681,7 @@
       </c>
       <c r="U7" s="24">
         <f ca="1">_xlfn.XLOOKUP(Q7,Winnings!$A$5:$A$39,Winnings!$U$5:$U$39)</f>
-        <v>110</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="8" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -3678,7 +3690,7 @@
       </c>
       <c r="B8" s="21" t="str">
         <f ca="1">IFERROR(INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B8)),"")</f>
-        <v>SaleeNmd</v>
+        <v>Waffle Hauss</v>
       </c>
       <c r="C8" s="21">
         <f t="array" aca="1" ref="C8" ca="1">IF(B8="","",INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B8)))</f>
@@ -3686,19 +3698,19 @@
       </c>
       <c r="D8" s="21">
         <f t="array" aca="1" ref="D8" ca="1">IF(B8="","",INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$C$10:$C$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B8)))</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E8" s="23">
         <f t="shared" ca="1" si="0"/>
-        <v>0.8125</v>
+        <v>0.75</v>
       </c>
       <c r="F8" s="21">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" s="24">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8" s="16"/>
       <c r="I8" t="s">
@@ -3706,7 +3718,7 @@
       </c>
       <c r="J8">
         <f ca="1">_xlfn.XLOOKUP(I8,Season!$A$5:$A$39,Season!$X$5:$X$39)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K8">
         <f ca="1">_xlfn.XLOOKUP(I8,Season!$A$5:$A$39,Season!$V$5:$V$39)</f>
@@ -3714,7 +3726,7 @@
       </c>
       <c r="L8">
         <f ca="1">_xlfn.XLOOKUP(I8,Season!$A$5:$A$39,Season!$U$5:$U$39)</f>
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="M8" s="29">
         <f ca="1">IF(_xlfn.XLOOKUP(I8,Winnings!A5:A39,Winnings!U5:U39)&gt;0,_xlfn.XLOOKUP(I8,Winnings!A5:A39,Winnings!U5:U39),0)</f>
@@ -3730,11 +3742,11 @@
       </c>
       <c r="R8" s="21">
         <f t="array" aca="1" ref="R8" ca="1">_xlfn.XLOOKUP(Q8,Table2[Player],Season!$T$5:$T$39)</f>
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="S8" s="23">
         <f ca="1">IFERROR(SUM(_xlfn.XLOOKUP(Q8,Table2[Player],Table2[Season Wins]))/SUM(Season!$B$3:$S$3),0)</f>
-        <v>9.5588235294117641E-2</v>
+        <v>9.1911764705882359E-2</v>
       </c>
       <c r="T8" s="21">
         <f t="shared" ca="1" si="3"/>
@@ -3751,7 +3763,7 @@
       </c>
       <c r="B9" s="21" t="str">
         <f ca="1">IFERROR(INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B9)),"")</f>
-        <v>FMF Doc</v>
+        <v>SaleeNmd</v>
       </c>
       <c r="C9" s="21">
         <f t="array" aca="1" ref="C9" ca="1">IF(B9="","",INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B9)))</f>
@@ -3767,11 +3779,11 @@
       </c>
       <c r="F9" s="21">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G9" s="24">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H9" s="16"/>
       <c r="I9" t="s">
@@ -3783,15 +3795,15 @@
       </c>
       <c r="K9">
         <f ca="1">_xlfn.XLOOKUP(I9,Season!$A$5:$A$39,Season!$V$5:$V$39)</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L9">
         <f ca="1">_xlfn.XLOOKUP(I9,Season!$A$5:$A$39,Season!$U$5:$U$39)</f>
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="M9" s="29">
         <f ca="1">IF(_xlfn.XLOOKUP(I9,Winnings!A6:A40,Winnings!U6:U40)&gt;0,_xlfn.XLOOKUP(I9,Winnings!A6:A40,Winnings!U6:U40),0)</f>
-        <v>110</v>
+        <v>35.5</v>
       </c>
       <c r="O9" s="16"/>
       <c r="P9" s="21">
@@ -3803,11 +3815,11 @@
       </c>
       <c r="R9" s="21">
         <f t="array" aca="1" ref="R9" ca="1">_xlfn.XLOOKUP(Q9,Table2[Player],Season!$T$5:$T$39)</f>
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="S9" s="23">
         <f ca="1">IFERROR(SUM(_xlfn.XLOOKUP(Q9,Table2[Player],Table2[Season Wins]))/SUM(Season!$B$3:$S$3),0)</f>
-        <v>9.1911764705882359E-2</v>
+        <v>8.8235294117647065E-2</v>
       </c>
       <c r="T9" s="21">
         <f t="shared" ca="1" si="3"/>
@@ -3824,19 +3836,19 @@
       </c>
       <c r="B10" s="21" t="str">
         <f ca="1">IFERROR(INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B10)),"")</f>
-        <v>Regltr5</v>
+        <v>MiMi</v>
       </c>
       <c r="C10" s="21">
         <f t="array" aca="1" ref="C10" ca="1">IF(B10="","",INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B10)))</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D10" s="21">
         <f t="array" aca="1" ref="D10" ca="1">IF(B10="","",INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$C$10:$C$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B10)))</f>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E10" s="23">
         <f t="shared" ca="1" si="0"/>
-        <v>0.75</v>
+        <v>0.625</v>
       </c>
       <c r="F10" s="21">
         <f t="shared" ca="1" si="1"/>
@@ -3852,7 +3864,7 @@
       </c>
       <c r="J10">
         <f ca="1">_xlfn.XLOOKUP(I10,Season!$A$5:$A$39,Season!$X$5:$X$39)</f>
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K10">
         <f ca="1">_xlfn.XLOOKUP(I10,Season!$A$5:$A$39,Season!$V$5:$V$39)</f>
@@ -3872,15 +3884,15 @@
       </c>
       <c r="Q10" s="21" t="str">
         <f ca="1">_xlfn.XLOOKUP(P10,Table2[Rank],Table2[Player])</f>
-        <v>FMF Doc</v>
+        <v>Phelpy</v>
       </c>
       <c r="R10" s="21">
         <f t="array" aca="1" ref="R10" ca="1">_xlfn.XLOOKUP(Q10,Table2[Player],Season!$T$5:$T$39)</f>
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="S10" s="23">
         <f ca="1">IFERROR(SUM(_xlfn.XLOOKUP(Q10,Table2[Player],Table2[Season Wins]))/SUM(Season!$B$3:$S$3),0)</f>
-        <v>9.1911764705882359E-2</v>
+        <v>8.8235294117647065E-2</v>
       </c>
       <c r="T10" s="21">
         <f t="shared" ca="1" si="3"/>
@@ -3888,7 +3900,7 @@
       </c>
       <c r="U10" s="24">
         <f ca="1">_xlfn.XLOOKUP(Q10,Winnings!$A$5:$A$39,Winnings!$U$5:$U$39)</f>
-        <v>-40</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -3897,27 +3909,27 @@
       </c>
       <c r="B11" s="21" t="str">
         <f ca="1">IFERROR(INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B11)),"")</f>
-        <v>Waffle Hauss</v>
+        <v>DPSOG</v>
       </c>
       <c r="C11" s="21">
         <f t="array" aca="1" ref="C11" ca="1">IF(B11="","",INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B11)))</f>
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D11" s="21">
         <f t="array" aca="1" ref="D11" ca="1">IF(B11="","",INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$C$10:$C$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B11)))</f>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E11" s="23">
         <f t="shared" ca="1" si="0"/>
-        <v>0.75</v>
+        <v>0.625</v>
       </c>
       <c r="F11" s="21">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G11" s="24">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H11" s="16"/>
       <c r="I11" t="s">
@@ -3925,7 +3937,7 @@
       </c>
       <c r="J11">
         <f ca="1">_xlfn.XLOOKUP(I11,Season!$A$5:$A$39,Season!$X$5:$X$39)</f>
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K11">
         <f ca="1">_xlfn.XLOOKUP(I11,Season!$A$5:$A$39,Season!$V$5:$V$39)</f>
@@ -3933,7 +3945,7 @@
       </c>
       <c r="L11">
         <f ca="1">_xlfn.XLOOKUP(I11,Season!$A$5:$A$39,Season!$U$5:$U$39)</f>
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="M11" s="29">
         <f ca="1">IF(_xlfn.XLOOKUP(I11,Winnings!A8:A42,Winnings!U8:U42)&gt;0,_xlfn.XLOOKUP(I11,Winnings!A8:A42,Winnings!U8:U42),0)</f>
@@ -3945,23 +3957,23 @@
       </c>
       <c r="Q11" s="21" t="str">
         <f ca="1">_xlfn.XLOOKUP(P11,Table2[Rank],Table2[Player])</f>
-        <v>Phelpy</v>
+        <v>FMF Doc</v>
       </c>
       <c r="R11" s="21">
         <f t="array" aca="1" ref="R11" ca="1">_xlfn.XLOOKUP(Q11,Table2[Player],Season!$T$5:$T$39)</f>
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="S11" s="23">
         <f ca="1">IFERROR(SUM(_xlfn.XLOOKUP(Q11,Table2[Player],Table2[Season Wins]))/SUM(Season!$B$3:$S$3),0)</f>
-        <v>9.1911764705882359E-2</v>
+        <v>8.455882352941177E-2</v>
       </c>
       <c r="T11" s="21">
         <f t="shared" ca="1" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U11" s="24">
         <f ca="1">_xlfn.XLOOKUP(Q11,Winnings!$A$5:$A$39,Winnings!$U$5:$U$39)</f>
-        <v>76</v>
+        <v>-40</v>
       </c>
     </row>
     <row r="12" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -3970,19 +3982,19 @@
       </c>
       <c r="B12" s="21" t="str">
         <f ca="1">IFERROR(INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B12)),"")</f>
-        <v>DPSOG</v>
+        <v>FMF Doc</v>
       </c>
       <c r="C12" s="21">
         <f t="array" aca="1" ref="C12" ca="1">IF(B12="","",INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B12)))</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D12" s="21">
         <f t="array" aca="1" ref="D12" ca="1">IF(B12="","",INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$C$10:$C$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B12)))</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E12" s="23">
         <f t="shared" ca="1" si="0"/>
-        <v>0.6875</v>
+        <v>0.625</v>
       </c>
       <c r="F12" s="21">
         <f t="shared" ca="1" si="1"/>
@@ -3998,15 +4010,15 @@
       </c>
       <c r="J12">
         <f ca="1">_xlfn.XLOOKUP(I12,Season!$A$5:$A$39,Season!$X$5:$X$39)</f>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K12">
         <f ca="1">_xlfn.XLOOKUP(I12,Season!$A$5:$A$39,Season!$V$5:$V$39)</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L12">
         <f ca="1">_xlfn.XLOOKUP(I12,Season!$A$5:$A$39,Season!$U$5:$U$39)</f>
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="M12" s="29">
         <f ca="1">IF(_xlfn.XLOOKUP(I12,Winnings!A9:A43,Winnings!U9:U43)&gt;0,_xlfn.XLOOKUP(I12,Winnings!A9:A43,Winnings!U9:U43),0)</f>
@@ -4018,19 +4030,19 @@
       </c>
       <c r="Q12" s="21" t="str">
         <f ca="1">_xlfn.XLOOKUP(P12,Table2[Rank],Table2[Player])</f>
-        <v>Regltr5</v>
+        <v>MiMi</v>
       </c>
       <c r="R12" s="21">
         <f t="array" aca="1" ref="R12" ca="1">_xlfn.XLOOKUP(Q12,Table2[Player],Season!$T$5:$T$39)</f>
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="S12" s="23">
         <f ca="1">IFERROR(SUM(_xlfn.XLOOKUP(Q12,Table2[Player],Table2[Season Wins]))/SUM(Season!$B$3:$S$3),0)</f>
-        <v>9.1911764705882359E-2</v>
+        <v>8.455882352941177E-2</v>
       </c>
       <c r="T12" s="21">
         <f t="shared" ca="1" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U12" s="24">
         <f ca="1">_xlfn.XLOOKUP(Q12,Winnings!$A$5:$A$39,Winnings!$U$5:$U$39)</f>
@@ -4043,19 +4055,19 @@
       </c>
       <c r="B13" s="21" t="str">
         <f ca="1">IFERROR(INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B13)),"")</f>
-        <v>MiMi</v>
+        <v>Regltr5</v>
       </c>
       <c r="C13" s="21">
         <f t="array" aca="1" ref="C13" ca="1">IF(B13="","",INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B13)))</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D13" s="21">
         <f t="array" aca="1" ref="D13" ca="1">IF(B13="","",INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$C$10:$C$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B13)))</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E13" s="23">
         <f t="shared" ca="1" si="0"/>
-        <v>0.6875</v>
+        <v>0.625</v>
       </c>
       <c r="F13" s="21">
         <f t="shared" ca="1" si="1"/>
@@ -4072,7 +4084,7 @@
       </c>
       <c r="Q13" s="21" t="str">
         <f ca="1">_xlfn.XLOOKUP(P13,Table2[Rank],Table2[Player])</f>
-        <v>Jim T</v>
+        <v>Phelps Phamily</v>
       </c>
       <c r="R13" s="21">
         <f t="array" aca="1" ref="R13" ca="1">_xlfn.XLOOKUP(Q13,Table2[Player],Season!$T$5:$T$39)</f>
@@ -4084,7 +4096,7 @@
       </c>
       <c r="T13" s="21">
         <f t="shared" ca="1" si="3"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U13" s="24">
         <f ca="1">_xlfn.XLOOKUP(Q13,Winnings!$A$5:$A$39,Winnings!$U$5:$U$39)</f>
@@ -4097,19 +4109,19 @@
       </c>
       <c r="B14" s="21" t="str">
         <f ca="1">IFERROR(INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B14)),"")</f>
-        <v>Navygolfer</v>
+        <v>Phelps Phamily</v>
       </c>
       <c r="C14" s="21">
         <f t="array" aca="1" ref="C14" ca="1">IF(B14="","",INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B14)))</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D14" s="21">
         <f t="array" aca="1" ref="D14" ca="1">IF(B14="","",INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$C$10:$C$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B14)))</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E14" s="23">
         <f t="shared" ca="1" si="0"/>
-        <v>0.6875</v>
+        <v>0.625</v>
       </c>
       <c r="F14" s="21">
         <f t="shared" ca="1" si="1"/>
@@ -4132,7 +4144,7 @@
       </c>
       <c r="Q14" s="21" t="str">
         <f ca="1">_xlfn.XLOOKUP(P14,Table2[Rank],Table2[Player])</f>
-        <v>MiMi</v>
+        <v>Regltr5</v>
       </c>
       <c r="R14" s="21">
         <f t="array" aca="1" ref="R14" ca="1">_xlfn.XLOOKUP(Q14,Table2[Player],Season!$T$5:$T$39)</f>
@@ -4144,7 +4156,7 @@
       </c>
       <c r="T14" s="21">
         <f t="shared" ca="1" si="3"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U14" s="24">
         <f ca="1">_xlfn.XLOOKUP(Q14,Winnings!$A$5:$A$39,Winnings!$U$5:$U$39)</f>
@@ -4161,15 +4173,15 @@
       </c>
       <c r="C15" s="21">
         <f t="array" aca="1" ref="C15" ca="1">IF(B15="","",INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B15)))</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D15" s="21">
         <f t="array" aca="1" ref="D15" ca="1">IF(B15="","",INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$C$10:$C$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B15)))</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E15" s="23">
         <f t="shared" ca="1" si="0"/>
-        <v>0.625</v>
+        <v>0.5625</v>
       </c>
       <c r="F15" s="21">
         <f t="shared" ca="1" si="1"/>
@@ -4185,7 +4197,7 @@
       </c>
       <c r="J15">
         <f ca="1">MAX(INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"))</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O15" s="16"/>
       <c r="P15" s="21">
@@ -4193,7 +4205,7 @@
       </c>
       <c r="Q15" s="21" t="str">
         <f ca="1">_xlfn.XLOOKUP(P15,Table2[Rank],Table2[Player])</f>
-        <v>Navygolfer</v>
+        <v>Waffle Hauss</v>
       </c>
       <c r="R15" s="21">
         <f t="array" aca="1" ref="R15" ca="1">_xlfn.XLOOKUP(Q15,Table2[Player],Season!$T$5:$T$39)</f>
@@ -4205,11 +4217,11 @@
       </c>
       <c r="T15" s="21">
         <f t="shared" ca="1" si="3"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U15" s="24">
         <f ca="1">_xlfn.XLOOKUP(Q15,Winnings!$A$5:$A$39,Winnings!$U$5:$U$39)</f>
-        <v>-40</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="16" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -4222,15 +4234,15 @@
       </c>
       <c r="C16" s="21">
         <f t="array" aca="1" ref="C16" ca="1">IF(B16="","",INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B16)))</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D16" s="21">
         <f t="array" aca="1" ref="D16" ca="1">IF(B16="","",INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$C$10:$C$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B16)))</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E16" s="23">
         <f t="shared" ca="1" si="0"/>
-        <v>0.6875</v>
+        <v>0.625</v>
       </c>
       <c r="F16" s="21">
         <f t="shared" ca="1" si="1"/>
@@ -4246,7 +4258,7 @@
       </c>
       <c r="J16">
         <f ca="1">_xlfn.MINIFS(INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),"&gt;=0")</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O16" s="16"/>
       <c r="P16" s="21">
@@ -4254,15 +4266,15 @@
       </c>
       <c r="Q16" s="21" t="str">
         <f ca="1">_xlfn.XLOOKUP(P16,Table2[Rank],Table2[Player])</f>
-        <v>Phelps Phamily</v>
+        <v>Jim T</v>
       </c>
       <c r="R16" s="21">
         <f t="array" aca="1" ref="R16" ca="1">_xlfn.XLOOKUP(Q16,Table2[Player],Season!$T$5:$T$39)</f>
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="S16" s="23">
         <f ca="1">IFERROR(SUM(_xlfn.XLOOKUP(Q16,Table2[Player],Table2[Season Wins]))/SUM(Season!$B$3:$S$3),0)</f>
-        <v>8.455882352941177E-2</v>
+        <v>8.0882352941176475E-2</v>
       </c>
       <c r="T16" s="21">
         <f t="shared" ca="1" si="3"/>
@@ -4283,15 +4295,15 @@
       </c>
       <c r="C17" s="21">
         <f t="array" aca="1" ref="C17" ca="1">IF(B17="","",INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B17)))</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D17" s="21">
         <f t="array" aca="1" ref="D17" ca="1">IF(B17="","",INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$C$10:$C$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B17)))</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E17" s="23">
         <f t="shared" ca="1" si="0"/>
-        <v>0.6875</v>
+        <v>0.625</v>
       </c>
       <c r="F17" s="21">
         <f t="shared" ca="1" si="1"/>
@@ -4307,7 +4319,7 @@
       </c>
       <c r="J17" s="4">
         <f ca="1">IFERROR(AVERAGEIF(INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),"&gt;=0"),0)</f>
-        <v>10.714285714285714</v>
+        <v>9.6857142857142851</v>
       </c>
       <c r="O17" s="16"/>
       <c r="P17" s="21">
@@ -4319,11 +4331,11 @@
       </c>
       <c r="R17" s="21">
         <f t="array" aca="1" ref="R17" ca="1">_xlfn.XLOOKUP(Q17,Table2[Player],Season!$T$5:$T$39)</f>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="S17" s="23">
         <f ca="1">IFERROR(SUM(_xlfn.XLOOKUP(Q17,Table2[Player],Table2[Season Wins]))/SUM(Season!$B$3:$S$3),0)</f>
-        <v>8.0882352941176475E-2</v>
+        <v>7.720588235294118E-2</v>
       </c>
       <c r="T17" s="21">
         <f t="shared" ca="1" si="3"/>
@@ -4344,15 +4356,15 @@
       </c>
       <c r="C18" s="21">
         <f t="array" aca="1" ref="C18" ca="1">IF(B18="","",INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B18)))</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D18" s="21">
         <f t="array" aca="1" ref="D18" ca="1">IF(B18="","",INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$C$10:$C$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B18)))</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E18" s="23">
         <f t="shared" ca="1" si="0"/>
-        <v>0.625</v>
+        <v>0.5625</v>
       </c>
       <c r="F18" s="21">
         <f t="shared" ca="1" si="1"/>
@@ -4368,7 +4380,7 @@
       </c>
       <c r="J18">
         <f ca="1">COUNTIF(INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),MAX(INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44")))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O18" s="16"/>
       <c r="P18" s="21">
@@ -4376,15 +4388,15 @@
       </c>
       <c r="Q18" s="21" t="str">
         <f ca="1">_xlfn.XLOOKUP(P18,Table2[Rank],Table2[Player])</f>
-        <v>cuetop</v>
+        <v>Frankethetank</v>
       </c>
       <c r="R18" s="21">
         <f t="array" aca="1" ref="R18" ca="1">_xlfn.XLOOKUP(Q18,Table2[Player],Season!$T$5:$T$39)</f>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="S18" s="23">
         <f ca="1">IFERROR(SUM(_xlfn.XLOOKUP(Q18,Table2[Player],Table2[Season Wins]))/SUM(Season!$B$3:$S$3),0)</f>
-        <v>8.0882352941176475E-2</v>
+        <v>7.720588235294118E-2</v>
       </c>
       <c r="T18" s="21">
         <f t="shared" ca="1" si="3"/>
@@ -4405,15 +4417,15 @@
       </c>
       <c r="C19" s="21">
         <f t="array" aca="1" ref="C19" ca="1">IF(B19="","",INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B19)))</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D19" s="21">
         <f t="array" aca="1" ref="D19" ca="1">IF(B19="","",INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$C$10:$C$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B19)))</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E19" s="23">
         <f t="shared" ca="1" si="0"/>
-        <v>0.625</v>
+        <v>0.5625</v>
       </c>
       <c r="F19" s="21">
         <f t="shared" ca="1" si="1"/>
@@ -4429,7 +4441,7 @@
       </c>
       <c r="J19">
         <f ca="1">COUNTIF(INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),"&gt;"&amp;AVERAGE(INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44")))</f>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="O19" s="16"/>
       <c r="P19" s="21">
@@ -4437,15 +4449,15 @@
       </c>
       <c r="Q19" s="21" t="str">
         <f ca="1">_xlfn.XLOOKUP(P19,Table2[Rank],Table2[Player])</f>
-        <v>Frankethetank</v>
+        <v>Katie A</v>
       </c>
       <c r="R19" s="21">
         <f t="array" aca="1" ref="R19" ca="1">_xlfn.XLOOKUP(Q19,Table2[Player],Season!$T$5:$T$39)</f>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="S19" s="23">
         <f ca="1">IFERROR(SUM(_xlfn.XLOOKUP(Q19,Table2[Player],Table2[Season Wins]))/SUM(Season!$B$3:$S$3),0)</f>
-        <v>8.0882352941176475E-2</v>
+        <v>7.720588235294118E-2</v>
       </c>
       <c r="T19" s="21">
         <f t="shared" ca="1" si="3"/>
@@ -4462,19 +4474,19 @@
       </c>
       <c r="B20" s="21" t="str">
         <f ca="1">IFERROR(INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B20)),"")</f>
-        <v>Phelps Phamily</v>
+        <v>Stan</v>
       </c>
       <c r="C20" s="21">
         <f t="array" aca="1" ref="C20" ca="1">IF(B20="","",INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B20)))</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D20" s="21">
         <f t="array" aca="1" ref="D20" ca="1">IF(B20="","",INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$C$10:$C$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B20)))</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E20" s="23">
         <f t="shared" ca="1" si="0"/>
-        <v>0.625</v>
+        <v>0.5625</v>
       </c>
       <c r="F20" s="21">
         <f t="shared" ca="1" si="1"/>
@@ -4497,15 +4509,15 @@
       </c>
       <c r="Q20" s="21" t="str">
         <f ca="1">_xlfn.XLOOKUP(P20,Table2[Rank],Table2[Player])</f>
-        <v>Katie A</v>
+        <v>Navygolfer</v>
       </c>
       <c r="R20" s="21">
         <f t="array" aca="1" ref="R20" ca="1">_xlfn.XLOOKUP(Q20,Table2[Player],Season!$T$5:$T$39)</f>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="S20" s="23">
         <f ca="1">IFERROR(SUM(_xlfn.XLOOKUP(Q20,Table2[Player],Table2[Season Wins]))/SUM(Season!$B$3:$S$3),0)</f>
-        <v>8.0882352941176475E-2</v>
+        <v>7.720588235294118E-2</v>
       </c>
       <c r="T20" s="21">
         <f t="shared" ca="1" si="3"/>
@@ -4522,11 +4534,11 @@
       </c>
       <c r="B21" s="21" t="str">
         <f ca="1">IFERROR(INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B21)),"")</f>
-        <v>Stan</v>
+        <v>Frankethetank</v>
       </c>
       <c r="C21" s="21">
         <f t="array" aca="1" ref="C21" ca="1">IF(B21="","",INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B21)))</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D21" s="21">
         <f t="array" aca="1" ref="D21" ca="1">IF(B21="","",INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$C$10:$C$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B21)))</f>
@@ -4562,11 +4574,11 @@
       </c>
       <c r="R21" s="21">
         <f t="array" aca="1" ref="R21" ca="1">_xlfn.XLOOKUP(Q21,Table2[Player],Season!$T$5:$T$39)</f>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="S21" s="23">
         <f ca="1">IFERROR(SUM(_xlfn.XLOOKUP(Q21,Table2[Player],Table2[Season Wins]))/SUM(Season!$B$3:$S$3),0)</f>
-        <v>8.0882352941176475E-2</v>
+        <v>7.720588235294118E-2</v>
       </c>
       <c r="T21" s="21">
         <f t="shared" ca="1" si="3"/>
@@ -4583,19 +4595,19 @@
       </c>
       <c r="B22" s="21" t="str">
         <f ca="1">IFERROR(INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B22)),"")</f>
-        <v>cuetop</v>
+        <v>Navygolfer</v>
       </c>
       <c r="C22" s="21">
         <f t="array" aca="1" ref="C22" ca="1">IF(B22="","",INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B22)))</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D22" s="21">
         <f t="array" aca="1" ref="D22" ca="1">IF(B22="","",INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$C$10:$C$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B22)))</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E22" s="23">
         <f t="shared" ca="1" si="0"/>
-        <v>0.625</v>
+        <v>0.5625</v>
       </c>
       <c r="F22" s="21">
         <f t="shared" ca="1" si="1"/>
@@ -4623,11 +4635,11 @@
       </c>
       <c r="R22" s="21">
         <f t="array" aca="1" ref="R22" ca="1">_xlfn.XLOOKUP(Q22,Table2[Player],Season!$T$5:$T$39)</f>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="S22" s="23">
         <f ca="1">IFERROR(SUM(_xlfn.XLOOKUP(Q22,Table2[Player],Table2[Season Wins]))/SUM(Season!$B$3:$S$3),0)</f>
-        <v>8.0882352941176475E-2</v>
+        <v>7.720588235294118E-2</v>
       </c>
       <c r="T22" s="21">
         <f t="shared" ca="1" si="3"/>
@@ -4644,19 +4656,19 @@
       </c>
       <c r="B23" s="21" t="str">
         <f ca="1">IFERROR(INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B23)),"")</f>
-        <v>Frankethetank</v>
+        <v>Samsaunt</v>
       </c>
       <c r="C23" s="21">
         <f t="array" aca="1" ref="C23" ca="1">IF(B23="","",INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B23)))</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D23" s="21">
         <f t="array" aca="1" ref="D23" ca="1">IF(B23="","",INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$C$10:$C$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B23)))</f>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E23" s="23">
         <f t="shared" ca="1" si="0"/>
-        <v>0.6875</v>
+        <v>0.5625</v>
       </c>
       <c r="F23" s="21">
         <f t="shared" ca="1" si="1"/>
@@ -4684,11 +4696,11 @@
       </c>
       <c r="R23" s="21">
         <f t="array" aca="1" ref="R23" ca="1">_xlfn.XLOOKUP(Q23,Table2[Player],Season!$T$5:$T$39)</f>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="S23" s="23">
         <f ca="1">IFERROR(SUM(_xlfn.XLOOKUP(Q23,Table2[Player],Table2[Season Wins]))/SUM(Season!$B$3:$S$3),0)</f>
-        <v>8.0882352941176475E-2</v>
+        <v>7.720588235294118E-2</v>
       </c>
       <c r="T23" s="21">
         <f t="shared" ca="1" si="3"/>
@@ -4705,19 +4717,19 @@
       </c>
       <c r="B24" s="21" t="str">
         <f ca="1">IFERROR(INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B24)),"")</f>
-        <v>Samsaunt</v>
+        <v>Gr8granpa</v>
       </c>
       <c r="C24" s="21">
         <f t="array" aca="1" ref="C24" ca="1">IF(B24="","",INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B24)))</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D24" s="21">
         <f t="array" aca="1" ref="D24" ca="1">IF(B24="","",INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$C$10:$C$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B24)))</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E24" s="23">
         <f t="shared" ca="1" si="0"/>
-        <v>0.625</v>
+        <v>0.5625</v>
       </c>
       <c r="F24" s="21">
         <f t="shared" ca="1" si="1"/>
@@ -4741,19 +4753,19 @@
       </c>
       <c r="Q24" s="21" t="str">
         <f ca="1">_xlfn.XLOOKUP(P24,Table2[Rank],Table2[Player])</f>
-        <v>Waffle Hauss</v>
+        <v>cuetop</v>
       </c>
       <c r="R24" s="21">
         <f t="array" aca="1" ref="R24" ca="1">_xlfn.XLOOKUP(Q24,Table2[Player],Season!$T$5:$T$39)</f>
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="S24" s="23">
         <f ca="1">IFERROR(SUM(_xlfn.XLOOKUP(Q24,Table2[Player],Table2[Season Wins]))/SUM(Season!$B$3:$S$3),0)</f>
-        <v>8.0882352941176475E-2</v>
+        <v>7.3529411764705885E-2</v>
       </c>
       <c r="T24" s="21">
         <f t="shared" ca="1" si="3"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U24" s="24">
         <f ca="1">_xlfn.XLOOKUP(Q24,Winnings!$A$5:$A$39,Winnings!$U$5:$U$39)</f>
@@ -4766,19 +4778,19 @@
       </c>
       <c r="B25" s="21" t="str">
         <f ca="1">IFERROR(INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B25)),"")</f>
-        <v>Gr8granpa</v>
+        <v>Mrp4real</v>
       </c>
       <c r="C25" s="21">
         <f t="array" aca="1" ref="C25" ca="1">IF(B25="","",INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B25)))</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D25" s="21">
         <f t="array" aca="1" ref="D25" ca="1">IF(B25="","",INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$C$10:$C$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B25)))</f>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E25" s="23">
         <f t="shared" ca="1" si="0"/>
-        <v>0.625</v>
+        <v>0.5</v>
       </c>
       <c r="F25" s="21">
         <f t="shared" ca="1" si="1"/>
@@ -4802,19 +4814,19 @@
       </c>
       <c r="Q25" s="21" t="str">
         <f ca="1">_xlfn.XLOOKUP(P25,Table2[Rank],Table2[Player])</f>
-        <v>Zach N</v>
+        <v>Gr8granpa</v>
       </c>
       <c r="R25" s="21">
         <f t="array" aca="1" ref="R25" ca="1">_xlfn.XLOOKUP(Q25,Table2[Player],Season!$T$5:$T$39)</f>
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="S25" s="23">
         <f ca="1">IFERROR(SUM(_xlfn.XLOOKUP(Q25,Table2[Player],Table2[Season Wins]))/SUM(Season!$B$3:$S$3),0)</f>
-        <v>8.0882352941176475E-2</v>
+        <v>7.3529411764705885E-2</v>
       </c>
       <c r="T25" s="21">
         <f t="shared" ca="1" si="3"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U25" s="24">
         <f ca="1">_xlfn.XLOOKUP(Q25,Winnings!$A$5:$A$39,Winnings!$U$5:$U$39)</f>
@@ -4827,11 +4839,11 @@
       </c>
       <c r="B26" s="21" t="str">
         <f ca="1">IFERROR(INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B26)),"")</f>
-        <v>Mrp4real</v>
+        <v>Ddupuy</v>
       </c>
       <c r="C26" s="21">
         <f t="array" aca="1" ref="C26" ca="1">IF(B26="","",INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B26)))</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D26" s="21">
         <f t="array" aca="1" ref="D26" ca="1">IF(B26="","",INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$C$10:$C$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B26)))</f>
@@ -4863,15 +4875,15 @@
       </c>
       <c r="Q26" s="21" t="str">
         <f ca="1">_xlfn.XLOOKUP(P26,Table2[Rank],Table2[Player])</f>
-        <v>Gr8granpa</v>
+        <v>meatloaf</v>
       </c>
       <c r="R26" s="21">
         <f t="array" aca="1" ref="R26" ca="1">_xlfn.XLOOKUP(Q26,Table2[Player],Season!$T$5:$T$39)</f>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S26" s="23">
         <f ca="1">IFERROR(SUM(_xlfn.XLOOKUP(Q26,Table2[Player],Table2[Season Wins]))/SUM(Season!$B$3:$S$3),0)</f>
-        <v>7.720588235294118E-2</v>
+        <v>7.3529411764705885E-2</v>
       </c>
       <c r="T26" s="21">
         <f t="shared" ca="1" si="3"/>
@@ -4888,27 +4900,27 @@
       </c>
       <c r="B27" s="21" t="str">
         <f ca="1">IFERROR(INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B27)),"")</f>
-        <v>Ddupuy</v>
+        <v>tb</v>
       </c>
       <c r="C27" s="21">
         <f t="array" aca="1" ref="C27" ca="1">IF(B27="","",INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B27)))</f>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D27" s="21">
         <f t="array" aca="1" ref="D27" ca="1">IF(B27="","",INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$C$10:$C$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B27)))</f>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E27" s="23">
         <f t="shared" ca="1" si="0"/>
-        <v>0.625</v>
+        <v>0.5</v>
       </c>
       <c r="F27" s="21">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G27" s="24">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H27" s="16"/>
       <c r="I27" t="s">
@@ -4924,15 +4936,15 @@
       </c>
       <c r="Q27" s="21" t="str">
         <f ca="1">_xlfn.XLOOKUP(P27,Table2[Rank],Table2[Player])</f>
-        <v>meatloaf</v>
+        <v>Samsaunt</v>
       </c>
       <c r="R27" s="21">
         <f t="array" aca="1" ref="R27" ca="1">_xlfn.XLOOKUP(Q27,Table2[Player],Season!$T$5:$T$39)</f>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S27" s="23">
         <f ca="1">IFERROR(SUM(_xlfn.XLOOKUP(Q27,Table2[Player],Table2[Season Wins]))/SUM(Season!$B$3:$S$3),0)</f>
-        <v>7.720588235294118E-2</v>
+        <v>7.3529411764705885E-2</v>
       </c>
       <c r="T27" s="21">
         <f t="shared" ca="1" si="3"/>
@@ -4949,19 +4961,19 @@
       </c>
       <c r="B28" s="21" t="str">
         <f ca="1">IFERROR(INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B28)),"")</f>
-        <v>tb</v>
+        <v>Katie A</v>
       </c>
       <c r="C28" s="21">
         <f t="array" aca="1" ref="C28" ca="1">IF(B28="","",INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B28)))</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D28" s="21">
         <f t="array" aca="1" ref="D28" ca="1">IF(B28="","",INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$C$10:$C$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B28)))</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E28" s="23">
         <f t="shared" ca="1" si="0"/>
-        <v>0.5625</v>
+        <v>0.5</v>
       </c>
       <c r="F28" s="21">
         <f t="shared" ca="1" si="1"/>
@@ -4985,15 +4997,15 @@
       </c>
       <c r="Q28" s="21" t="str">
         <f ca="1">_xlfn.XLOOKUP(P28,Table2[Rank],Table2[Player])</f>
-        <v>Samsaunt</v>
+        <v>Vonasek Family</v>
       </c>
       <c r="R28" s="21">
         <f t="array" aca="1" ref="R28" ca="1">_xlfn.XLOOKUP(Q28,Table2[Player],Season!$T$5:$T$39)</f>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S28" s="23">
         <f ca="1">IFERROR(SUM(_xlfn.XLOOKUP(Q28,Table2[Player],Table2[Season Wins]))/SUM(Season!$B$3:$S$3),0)</f>
-        <v>7.720588235294118E-2</v>
+        <v>7.3529411764705885E-2</v>
       </c>
       <c r="T28" s="21">
         <f t="shared" ca="1" si="3"/>
@@ -5010,19 +5022,19 @@
       </c>
       <c r="B29" s="21" t="str">
         <f ca="1">IFERROR(INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B29)),"")</f>
-        <v>Katie A</v>
+        <v>meatloaf</v>
       </c>
       <c r="C29" s="21">
         <f t="array" aca="1" ref="C29" ca="1">IF(B29="","",INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B29)))</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D29" s="21">
         <f t="array" aca="1" ref="D29" ca="1">IF(B29="","",INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$C$10:$C$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B29)))</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E29" s="23">
         <f t="shared" ca="1" si="0"/>
-        <v>0.5625</v>
+        <v>0.5</v>
       </c>
       <c r="F29" s="21">
         <f t="shared" ca="1" si="1"/>
@@ -5046,15 +5058,15 @@
       </c>
       <c r="Q29" s="21" t="str">
         <f ca="1">_xlfn.XLOOKUP(P29,Table2[Rank],Table2[Player])</f>
-        <v>Vonasek Family</v>
+        <v>Zach N</v>
       </c>
       <c r="R29" s="21">
         <f t="array" aca="1" ref="R29" ca="1">_xlfn.XLOOKUP(Q29,Table2[Player],Season!$T$5:$T$39)</f>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S29" s="23">
         <f ca="1">IFERROR(SUM(_xlfn.XLOOKUP(Q29,Table2[Player],Table2[Season Wins]))/SUM(Season!$B$3:$S$3),0)</f>
-        <v>7.720588235294118E-2</v>
+        <v>7.3529411764705885E-2</v>
       </c>
       <c r="T29" s="21">
         <f t="shared" ca="1" si="3"/>
@@ -5071,19 +5083,19 @@
       </c>
       <c r="B30" s="21" t="str">
         <f ca="1">IFERROR(INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B30)),"")</f>
-        <v>meatloaf</v>
+        <v>Vonasek Family</v>
       </c>
       <c r="C30" s="21">
         <f t="array" aca="1" ref="C30" ca="1">IF(B30="","",INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B30)))</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D30" s="21">
         <f t="array" aca="1" ref="D30" ca="1">IF(B30="","",INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$C$10:$C$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B30)))</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E30" s="23">
         <f t="shared" ca="1" si="0"/>
-        <v>0.5625</v>
+        <v>0.5</v>
       </c>
       <c r="F30" s="21">
         <f t="shared" ca="1" si="1"/>
@@ -5111,11 +5123,11 @@
       </c>
       <c r="R30" s="21">
         <f t="array" aca="1" ref="R30" ca="1">_xlfn.XLOOKUP(Q30,Table2[Player],Season!$T$5:$T$39)</f>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="S30" s="23">
         <f ca="1">IFERROR(SUM(_xlfn.XLOOKUP(Q30,Table2[Player],Table2[Season Wins]))/SUM(Season!$B$3:$S$3),0)</f>
-        <v>7.3529411764705885E-2</v>
+        <v>6.985294117647059E-2</v>
       </c>
       <c r="T30" s="21">
         <f t="shared" ca="1" si="3"/>
@@ -5132,19 +5144,19 @@
       </c>
       <c r="B31" s="21" t="str">
         <f ca="1">IFERROR(INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B31)),"")</f>
-        <v>Vonasek Family</v>
+        <v>cuetop</v>
       </c>
       <c r="C31" s="21">
         <f t="array" aca="1" ref="C31" ca="1">IF(B31="","",INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B31)))</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D31" s="21">
         <f t="array" aca="1" ref="D31" ca="1">IF(B31="","",INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$C$10:$C$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B31)))</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E31" s="23">
         <f t="shared" ca="1" si="0"/>
-        <v>0.5625</v>
+        <v>0.5</v>
       </c>
       <c r="F31" s="21">
         <f t="shared" ca="1" si="1"/>
@@ -5168,15 +5180,15 @@
       </c>
       <c r="Q31" s="21" t="str">
         <f ca="1">_xlfn.XLOOKUP(P31,Table2[Rank],Table2[Player])</f>
-        <v>Debe</v>
+        <v>MayeDay! MayeDay!</v>
       </c>
       <c r="R31" s="21">
         <f t="array" aca="1" ref="R31" ca="1">_xlfn.XLOOKUP(Q31,Table2[Player],Season!$T$5:$T$39)</f>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="S31" s="23">
         <f ca="1">IFERROR(SUM(_xlfn.XLOOKUP(Q31,Table2[Player],Table2[Season Wins]))/SUM(Season!$B$3:$S$3),0)</f>
-        <v>7.3529411764705885E-2</v>
+        <v>6.985294117647059E-2</v>
       </c>
       <c r="T31" s="21">
         <f t="shared" ca="1" si="3"/>
@@ -5197,15 +5209,15 @@
       </c>
       <c r="C32" s="21">
         <f t="array" aca="1" ref="C32" ca="1">IF(B32="","",INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B32)))</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D32" s="21">
         <f t="array" aca="1" ref="D32" ca="1">IF(B32="","",INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$C$10:$C$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B32)))</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E32" s="23">
         <f t="shared" ca="1" si="0"/>
-        <v>0.5625</v>
+        <v>0.5</v>
       </c>
       <c r="F32" s="21">
         <f t="shared" ca="1" si="1"/>
@@ -5229,19 +5241,19 @@
       </c>
       <c r="Q32" s="21" t="str">
         <f ca="1">_xlfn.XLOOKUP(P32,Table2[Rank],Table2[Player])</f>
-        <v>MayeDay! MayeDay!</v>
+        <v>Debe</v>
       </c>
       <c r="R32" s="21">
         <f t="array" aca="1" ref="R32" ca="1">_xlfn.XLOOKUP(Q32,Table2[Player],Season!$T$5:$T$39)</f>
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="S32" s="23">
         <f ca="1">IFERROR(SUM(_xlfn.XLOOKUP(Q32,Table2[Player],Table2[Season Wins]))/SUM(Season!$B$3:$S$3),0)</f>
-        <v>7.3529411764705885E-2</v>
+        <v>6.6176470588235295E-2</v>
       </c>
       <c r="T32" s="21">
         <f t="shared" ca="1" si="3"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U32" s="24">
         <f ca="1">_xlfn.XLOOKUP(Q32,Winnings!$A$5:$A$39,Winnings!$U$5:$U$39)</f>
@@ -5258,15 +5270,15 @@
       </c>
       <c r="C33" s="21">
         <f t="array" aca="1" ref="C33" ca="1">IF(B33="","",INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B33)))</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D33" s="21">
         <f t="array" aca="1" ref="D33" ca="1">IF(B33="","",INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$C$10:$C$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B33)))</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E33" s="23">
         <f t="shared" ca="1" si="0"/>
-        <v>0.625</v>
+        <v>0.5625</v>
       </c>
       <c r="F33" s="21">
         <f t="shared" ca="1" si="1"/>
@@ -5290,15 +5302,15 @@
       </c>
       <c r="Q33" s="21" t="str">
         <f ca="1">_xlfn.XLOOKUP(P33,Table2[Rank],Table2[Player])</f>
-        <v>Mrp4real</v>
+        <v>Ian</v>
       </c>
       <c r="R33" s="21">
         <f t="array" aca="1" ref="R33" ca="1">_xlfn.XLOOKUP(Q33,Table2[Player],Season!$T$5:$T$39)</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="S33" s="23">
         <f ca="1">IFERROR(SUM(_xlfn.XLOOKUP(Q33,Table2[Player],Table2[Season Wins]))/SUM(Season!$B$3:$S$3),0)</f>
-        <v>6.985294117647059E-2</v>
+        <v>6.6176470588235295E-2</v>
       </c>
       <c r="T33" s="21">
         <f t="shared" ca="1" si="3"/>
@@ -5315,19 +5327,19 @@
       </c>
       <c r="B34" s="21" t="str">
         <f ca="1">IFERROR(INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B34)),"")</f>
-        <v>Zach N</v>
+        <v>CraneGuy936</v>
       </c>
       <c r="C34" s="21">
         <f t="array" aca="1" ref="C34" ca="1">IF(B34="","",INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B34)))</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D34" s="21">
         <f t="array" aca="1" ref="D34" ca="1">IF(B34="","",INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$C$10:$C$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B34)))</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E34" s="23">
         <f t="shared" ca="1" si="0"/>
-        <v>0.5</v>
+        <v>0.4375</v>
       </c>
       <c r="F34" s="21">
         <f t="shared" ca="1" si="1"/>
@@ -5351,15 +5363,15 @@
       </c>
       <c r="Q34" s="21" t="str">
         <f ca="1">_xlfn.XLOOKUP(P34,Table2[Rank],Table2[Player])</f>
-        <v>Rusted Ox</v>
+        <v>Mrp4real</v>
       </c>
       <c r="R34" s="21">
         <f t="array" aca="1" ref="R34" ca="1">_xlfn.XLOOKUP(Q34,Table2[Player],Season!$T$5:$T$39)</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="S34" s="23">
         <f ca="1">IFERROR(SUM(_xlfn.XLOOKUP(Q34,Table2[Player],Table2[Season Wins]))/SUM(Season!$B$3:$S$3),0)</f>
-        <v>6.985294117647059E-2</v>
+        <v>6.6176470588235295E-2</v>
       </c>
       <c r="T34" s="21">
         <f t="shared" ca="1" si="3"/>
@@ -5376,19 +5388,19 @@
       </c>
       <c r="B35" s="21" t="str">
         <f ca="1">IFERROR(INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B35)),"")</f>
-        <v>Debe</v>
+        <v>Ian</v>
       </c>
       <c r="C35" s="21">
         <f t="array" aca="1" ref="C35" ca="1">IF(B35="","",INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B35)))</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D35" s="21">
         <f t="array" aca="1" ref="D35" ca="1">IF(B35="","",INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$C$10:$C$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B35)))</f>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E35" s="23">
         <f t="shared" ca="1" si="0"/>
-        <v>0.5625</v>
+        <v>0.4375</v>
       </c>
       <c r="F35" s="21">
         <f t="shared" ca="1" si="1"/>
@@ -5412,15 +5424,15 @@
       </c>
       <c r="Q35" s="21" t="str">
         <f ca="1">_xlfn.XLOOKUP(P35,Table2[Rank],Table2[Player])</f>
-        <v>The Dark Side</v>
+        <v>Rusted Ox</v>
       </c>
       <c r="R35" s="21">
         <f t="array" aca="1" ref="R35" ca="1">_xlfn.XLOOKUP(Q35,Table2[Player],Season!$T$5:$T$39)</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="S35" s="23">
         <f ca="1">IFERROR(SUM(_xlfn.XLOOKUP(Q35,Table2[Player],Table2[Season Wins]))/SUM(Season!$B$3:$S$3),0)</f>
-        <v>6.985294117647059E-2</v>
+        <v>6.6176470588235295E-2</v>
       </c>
       <c r="T35" s="21">
         <f t="shared" ca="1" si="3"/>
@@ -5437,19 +5449,19 @@
       </c>
       <c r="B36" s="21" t="str">
         <f ca="1">IFERROR(INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B36)),"")</f>
-        <v>CraneGuy936</v>
+        <v>Brick_Hauss</v>
       </c>
       <c r="C36" s="21">
         <f t="array" aca="1" ref="C36" ca="1">IF(B36="","",INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B36)))</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D36" s="21">
         <f t="array" aca="1" ref="D36" ca="1">IF(B36="","",INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$C$10:$C$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B36)))</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E36" s="23">
         <f t="shared" ca="1" si="0"/>
-        <v>0.5</v>
+        <v>0.4375</v>
       </c>
       <c r="F36" s="21">
         <f t="shared" ca="1" si="1"/>
@@ -5473,7 +5485,7 @@
       </c>
       <c r="Q36" s="21" t="str">
         <f ca="1">_xlfn.XLOOKUP(P36,Table2[Rank],Table2[Player])</f>
-        <v>Ddupuy</v>
+        <v>The Dark Side</v>
       </c>
       <c r="R36" s="21">
         <f t="array" aca="1" ref="R36" ca="1">_xlfn.XLOOKUP(Q36,Table2[Player],Season!$T$5:$T$39)</f>
@@ -5485,7 +5497,7 @@
       </c>
       <c r="T36" s="21">
         <f t="shared" ca="1" si="3"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U36" s="24">
         <f ca="1">_xlfn.XLOOKUP(Q36,Winnings!$A$5:$A$39,Winnings!$U$5:$U$39)</f>
@@ -5498,19 +5510,19 @@
       </c>
       <c r="B37" s="21" t="str">
         <f ca="1">IFERROR(INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B37)),"")</f>
-        <v>Ian</v>
+        <v>Zach N</v>
       </c>
       <c r="C37" s="21">
         <f t="array" aca="1" ref="C37" ca="1">IF(B37="","",INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B37)))</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D37" s="21">
         <f t="array" aca="1" ref="D37" ca="1">IF(B37="","",INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$C$10:$C$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B37)))</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E37" s="23">
         <f t="shared" ca="1" si="0"/>
-        <v>0.4375</v>
+        <v>0.375</v>
       </c>
       <c r="F37" s="21">
         <f t="shared" ca="1" si="1"/>
@@ -5534,15 +5546,15 @@
       </c>
       <c r="Q37" s="21" t="str">
         <f ca="1">_xlfn.XLOOKUP(P37,Table2[Rank],Table2[Player])</f>
-        <v>Ian</v>
+        <v>Ddupuy</v>
       </c>
       <c r="R37" s="21">
         <f t="array" aca="1" ref="R37" ca="1">_xlfn.XLOOKUP(Q37,Table2[Player],Season!$T$5:$T$39)</f>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="S37" s="23">
         <f ca="1">IFERROR(SUM(_xlfn.XLOOKUP(Q37,Table2[Player],Table2[Season Wins]))/SUM(Season!$B$3:$S$3),0)</f>
-        <v>6.6176470588235295E-2</v>
+        <v>6.25E-2</v>
       </c>
       <c r="T37" s="21">
         <f t="shared" ca="1" si="3"/>
@@ -5559,19 +5571,19 @@
       </c>
       <c r="B38" s="21" t="str">
         <f ca="1">IFERROR(INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B38)),"")</f>
-        <v>Ryan S</v>
+        <v>Debe</v>
       </c>
       <c r="C38" s="21">
         <f t="array" aca="1" ref="C38" ca="1">IF(B38="","",INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B38)))</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D38" s="21">
         <f t="array" aca="1" ref="D38" ca="1">IF(B38="","",INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$C$10:$C$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B38)))</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E38" s="23">
         <f t="shared" ca="1" si="0"/>
-        <v>0.5</v>
+        <v>0.4375</v>
       </c>
       <c r="F38" s="21">
         <f t="shared" ca="1" si="1"/>
@@ -5595,15 +5607,15 @@
       </c>
       <c r="Q38" s="21" t="str">
         <f ca="1">_xlfn.XLOOKUP(P38,Table2[Rank],Table2[Player])</f>
-        <v>Ryan S</v>
+        <v>TheDogfather</v>
       </c>
       <c r="R38" s="21">
         <f t="array" aca="1" ref="R38" ca="1">_xlfn.XLOOKUP(Q38,Table2[Player],Season!$T$5:$T$39)</f>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="S38" s="23">
         <f ca="1">IFERROR(SUM(_xlfn.XLOOKUP(Q38,Table2[Player],Table2[Season Wins]))/SUM(Season!$B$3:$S$3),0)</f>
-        <v>6.6176470588235295E-2</v>
+        <v>6.25E-2</v>
       </c>
       <c r="T38" s="21">
         <f t="shared" ca="1" si="3"/>
@@ -5624,15 +5636,15 @@
       </c>
       <c r="C39" s="21">
         <f t="array" aca="1" ref="C39" ca="1">IF(B39="","",INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B39)))</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D39" s="21">
         <f t="array" aca="1" ref="D39" ca="1">IF(B39="","",INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$C$10:$C$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B39)))</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E39" s="23">
         <f t="shared" ca="1" si="0"/>
-        <v>0.5</v>
+        <v>0.4375</v>
       </c>
       <c r="F39" s="21">
         <f t="shared" ca="1" si="1"/>
@@ -5649,19 +5661,19 @@
       </c>
       <c r="Q39" s="21" t="str">
         <f ca="1">_xlfn.XLOOKUP(P39,Table2[Rank],Table2[Player])</f>
-        <v>TheDogfather</v>
+        <v>Brick_Hauss</v>
       </c>
       <c r="R39" s="21">
         <f t="array" aca="1" ref="R39" ca="1">_xlfn.XLOOKUP(Q39,Table2[Player],Season!$T$5:$T$39)</f>
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="S39" s="23">
         <f ca="1">IFERROR(SUM(_xlfn.XLOOKUP(Q39,Table2[Player],Table2[Season Wins]))/SUM(Season!$B$3:$S$3),0)</f>
-        <v>6.6176470588235295E-2</v>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="T39" s="21">
         <f t="shared" ca="1" si="3"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="U39" s="24">
         <f ca="1">_xlfn.XLOOKUP(Q39,Winnings!$A$5:$A$39,Winnings!$U$5:$U$39)</f>
@@ -5674,27 +5686,27 @@
       </c>
       <c r="B40" s="21" t="str">
         <f ca="1">IFERROR(INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B40)),"")</f>
-        <v>Brick_Hauss</v>
+        <v>Ryan S</v>
       </c>
       <c r="C40" s="21">
         <f t="array" aca="1" ref="C40" ca="1">IF(B40="","",INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B40)))</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D40" s="21">
         <f t="array" aca="1" ref="D40" ca="1">IF(B40="","",INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$C$10:$C$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B40)))</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E40" s="23">
         <f t="shared" ca="1" si="0"/>
-        <v>0.4375</v>
+        <v>0.375</v>
       </c>
       <c r="F40" s="21">
         <f t="shared" ca="1" si="1"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G40" s="24">
         <f t="shared" ca="1" si="2"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H40" s="16"/>
       <c r="O40" s="16"/>
@@ -5703,7 +5715,7 @@
       </c>
       <c r="Q40" s="21" t="str">
         <f ca="1">_xlfn.XLOOKUP(P40,Table2[Rank],Table2[Player])</f>
-        <v>Brick_Hauss</v>
+        <v>Ryan S</v>
       </c>
       <c r="R40" s="21">
         <f t="array" aca="1" ref="R40" ca="1">_xlfn.XLOOKUP(Q40,Table2[Player],Season!$T$5:$T$39)</f>
@@ -5715,7 +5727,7 @@
       </c>
       <c r="T40" s="21">
         <f t="shared" ca="1" si="3"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="U40" s="24">
         <f ca="1">_xlfn.XLOOKUP(Q40,Winnings!$A$5:$A$39,Winnings!$U$5:$U$39)</f>
@@ -5732,15 +5744,15 @@
       </c>
       <c r="C41" s="21">
         <f t="array" aca="1" ref="C41" ca="1">IF(B41="","",INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B41)))</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D41" s="21">
         <f t="array" aca="1" ref="D41" ca="1">IF(B41="","",INDEX(_xlfn.SORTBY(INDIRECT("'"&amp;$A$1&amp;"'!$C$10:$C$44"),INDIRECT("'"&amp;$A$1&amp;"'!$B$10:$B$44"),-1),ROWS($B$7:B41)))</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E41" s="23">
         <f t="shared" ca="1" si="0"/>
-        <v>0.375</v>
+        <v>0.3125</v>
       </c>
       <c r="F41" s="21">
         <f t="shared" ca="1" si="1"/>
@@ -5761,11 +5773,11 @@
       </c>
       <c r="R41" s="21">
         <f t="array" aca="1" ref="R41" ca="1">_xlfn.XLOOKUP(Q41,Table2[Player],Season!$T$5:$T$39)</f>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="S41" s="23">
         <f ca="1">IFERROR(SUM(_xlfn.XLOOKUP(Q41,Table2[Player],Table2[Season Wins]))/SUM(Season!$B$3:$S$3),0)</f>
-        <v>5.8823529411764705E-2</v>
+        <v>5.514705882352941E-2</v>
       </c>
       <c r="T41" s="21">
         <f t="shared" ca="1" si="3"/>
@@ -5873,7 +5885,7 @@
   <sheetData>
     <row r="1" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A1" s="54" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B1" s="45"/>
       <c r="C1" s="45"/>
@@ -7525,7 +7537,7 @@
   <sheetData>
     <row r="1" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A1" s="54" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B1" s="45"/>
       <c r="C1" s="45"/>
@@ -9177,7 +9189,7 @@
   <sheetData>
     <row r="1" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A1" s="54" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B1" s="45"/>
       <c r="C1" s="45"/>
@@ -10829,7 +10841,7 @@
   <sheetData>
     <row r="1" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A1" s="54" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B1" s="45"/>
       <c r="C1" s="45"/>
@@ -12481,7 +12493,7 @@
   <sheetData>
     <row r="1" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A1" s="54" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B1" s="45"/>
       <c r="C1" s="45"/>
@@ -14133,7 +14145,7 @@
   <sheetData>
     <row r="1" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A1" s="54" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B1" s="45"/>
       <c r="C1" s="45"/>
@@ -15785,7 +15797,7 @@
   <sheetData>
     <row r="1" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A1" s="54" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B1" s="45"/>
       <c r="C1" s="45"/>
@@ -17437,7 +17449,7 @@
   <sheetData>
     <row r="1" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A1" s="54" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B1" s="45"/>
       <c r="C1" s="45"/>
@@ -19089,7 +19101,7 @@
   <sheetData>
     <row r="1" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A1" s="54" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B1" s="45"/>
       <c r="C1" s="45"/>
@@ -20741,7 +20753,7 @@
   <sheetData>
     <row r="1" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A1" s="54" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B1" s="45"/>
       <c r="C1" s="45"/>
@@ -22583,7 +22595,7 @@
       </c>
       <c r="C5" s="41">
         <f t="array" aca="1" ref="C5" ca="1">_xlfn.IFNA(_xlfn.XLOOKUP($A5,INDIRECT("'"&amp;C$4&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;C$4&amp;"'!$b$10:$b$44"))," ")</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D5" s="41" t="str">
         <f t="array" aca="1" ref="D5" ca="1">_xlfn.IFNA(_xlfn.XLOOKUP($A5,INDIRECT("'"&amp;D$4&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;D$4&amp;"'!$b$10:$b$44"))," ")</f>
@@ -22643,15 +22655,15 @@
       </c>
       <c r="T5" s="41">
         <f t="shared" ref="T5:T39" ca="1" si="0">SUM(B5:K5)</f>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="U5" s="19">
         <f t="shared" ref="U5:U39" ca="1" si="1">IFERROR(AVERAGEIF(B5:Q5,"&gt;=0"),0)</f>
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="V5" s="41">
         <f t="shared" ref="V5:V39" ca="1" si="2">IFERROR(MAX(B5:Q5),0)</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="W5" s="41">
         <f t="shared" ref="W5:W39" ca="1" si="3">IFERROR(_xlfn.MINIFS(B5:Q5,B5:Q5,"&gt;0"),0)</f>
@@ -22663,7 +22675,7 @@
       </c>
       <c r="Y5" s="34">
         <f t="array" aca="1" ref="Y5" ca="1">IFERROR(T5/SUMPRODUCT(($B5:$C5&lt;&gt;"")*$B$3:$C$3),0)</f>
-        <v>0.6875</v>
+        <v>0.65625</v>
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.3">
@@ -22752,7 +22764,7 @@
       </c>
       <c r="X6" s="41">
         <f ca="1">RANK(T6,$T$5:$T$39)+COUNTIF($T$5:T6,T6)-1</f>
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Y6" s="34">
         <f t="array" aca="1" ref="Y6" ca="1">IFERROR(T6/SUMPRODUCT(($B6:$C6&lt;&gt;"")*$B$3:$C$3),0)</f>
@@ -22769,7 +22781,7 @@
       </c>
       <c r="C7" s="41">
         <f t="array" aca="1" ref="C7" ca="1">_xlfn.IFNA(_xlfn.XLOOKUP($A7,INDIRECT("'"&amp;C$4&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;C$4&amp;"'!$b$10:$b$44"))," ")</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D7" s="41" t="str">
         <f t="array" aca="1" ref="D7" ca="1">_xlfn.IFNA(_xlfn.XLOOKUP($A7,INDIRECT("'"&amp;D$4&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;D$4&amp;"'!$b$10:$b$44"))," ")</f>
@@ -22829,11 +22841,11 @@
       </c>
       <c r="T7" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="U7" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="V7" s="41">
         <f t="shared" ca="1" si="2"/>
@@ -22841,7 +22853,7 @@
       </c>
       <c r="W7" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X7" s="41">
         <f ca="1">RANK(T7,$T$5:$T$39)+COUNTIF($T$5:T7,T7)-1</f>
@@ -22849,7 +22861,7 @@
       </c>
       <c r="Y7" s="34">
         <f t="array" aca="1" ref="Y7" ca="1">IFERROR(T7/SUMPRODUCT(($B7:$C7&lt;&gt;"")*$B$3:$C$3),0)</f>
-        <v>0.625</v>
+        <v>0.59375</v>
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.3">
@@ -22862,7 +22874,7 @@
       </c>
       <c r="C8" s="41">
         <f t="array" aca="1" ref="C8" ca="1">_xlfn.IFNA(_xlfn.XLOOKUP($A8,INDIRECT("'"&amp;C$4&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;C$4&amp;"'!$b$10:$b$44"))," ")</f>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D8" s="41" t="str">
         <f t="array" aca="1" ref="D8" ca="1">_xlfn.IFNA(_xlfn.XLOOKUP($A8,INDIRECT("'"&amp;D$4&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;D$4&amp;"'!$b$10:$b$44"))," ")</f>
@@ -22922,11 +22934,11 @@
       </c>
       <c r="T8" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="U8" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V8" s="41">
         <f t="shared" ca="1" si="2"/>
@@ -22934,15 +22946,15 @@
       </c>
       <c r="W8" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="X8" s="41">
         <f ca="1">RANK(T8,$T$5:$T$39)+COUNTIF($T$5:T8,T8)-1</f>
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="Y8" s="34">
         <f t="array" aca="1" ref="Y8" ca="1">IFERROR(T8/SUMPRODUCT(($B8:$C8&lt;&gt;"")*$B$3:$C$3),0)</f>
-        <v>0.6875</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.3">
@@ -22955,7 +22967,7 @@
       </c>
       <c r="C9" s="41">
         <f t="array" aca="1" ref="C9" ca="1">_xlfn.IFNA(_xlfn.XLOOKUP($A9,INDIRECT("'"&amp;C$4&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;C$4&amp;"'!$b$10:$b$44"))," ")</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D9" s="41" t="str">
         <f t="array" aca="1" ref="D9" ca="1">_xlfn.IFNA(_xlfn.XLOOKUP($A9,INDIRECT("'"&amp;D$4&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;D$4&amp;"'!$b$10:$b$44"))," ")</f>
@@ -23015,15 +23027,15 @@
       </c>
       <c r="T9" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="U9" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="V9" s="41">
         <f t="shared" ca="1" si="2"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="W9" s="41">
         <f t="shared" ca="1" si="3"/>
@@ -23031,11 +23043,11 @@
       </c>
       <c r="X9" s="41">
         <f ca="1">RANK(T9,$T$5:$T$39)+COUNTIF($T$5:T9,T9)-1</f>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="Y9" s="34">
         <f t="array" aca="1" ref="Y9" ca="1">IFERROR(T9/SUMPRODUCT(($B9:$C9&lt;&gt;"")*$B$3:$C$3),0)</f>
-        <v>0.5625</v>
+        <v>0.53125</v>
       </c>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.3">
@@ -23048,7 +23060,7 @@
       </c>
       <c r="C10" s="41">
         <f t="array" aca="1" ref="C10" ca="1">_xlfn.IFNA(_xlfn.XLOOKUP($A10,INDIRECT("'"&amp;C$4&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;C$4&amp;"'!$b$10:$b$44"))," ")</f>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D10" s="41" t="str">
         <f t="array" aca="1" ref="D10" ca="1">_xlfn.IFNA(_xlfn.XLOOKUP($A10,INDIRECT("'"&amp;D$4&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;D$4&amp;"'!$b$10:$b$44"))," ")</f>
@@ -23108,11 +23120,11 @@
       </c>
       <c r="T10" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="U10" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V10" s="41">
         <f t="shared" ca="1" si="2"/>
@@ -23120,15 +23132,15 @@
       </c>
       <c r="W10" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X10" s="41">
         <f ca="1">RANK(T10,$T$5:$T$39)+COUNTIF($T$5:T10,T10)-1</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Y10" s="34">
         <f t="array" aca="1" ref="Y10" ca="1">IFERROR(T10/SUMPRODUCT(($B10:$C10&lt;&gt;"")*$B$3:$C$3),0)</f>
-        <v>0.625</v>
+        <v>0.5625</v>
       </c>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.3">
@@ -23141,7 +23153,7 @@
       </c>
       <c r="C11" s="41">
         <f t="array" aca="1" ref="C11" ca="1">_xlfn.IFNA(_xlfn.XLOOKUP($A11,INDIRECT("'"&amp;C$4&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;C$4&amp;"'!$b$10:$b$44"))," ")</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D11" s="41" t="str">
         <f t="array" aca="1" ref="D11" ca="1">_xlfn.IFNA(_xlfn.XLOOKUP($A11,INDIRECT("'"&amp;D$4&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;D$4&amp;"'!$b$10:$b$44"))," ")</f>
@@ -23201,11 +23213,11 @@
       </c>
       <c r="T11" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="U11" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="V11" s="41">
         <f t="shared" ca="1" si="2"/>
@@ -23213,7 +23225,7 @@
       </c>
       <c r="W11" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="X11" s="41">
         <f ca="1">RANK(T11,$T$5:$T$39)+COUNTIF($T$5:T11,T11)-1</f>
@@ -23221,7 +23233,7 @@
       </c>
       <c r="Y11" s="34">
         <f t="array" aca="1" ref="Y11" ca="1">IFERROR(T11/SUMPRODUCT(($B11:$C11&lt;&gt;"")*$B$3:$C$3),0)</f>
-        <v>0.78125</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.3">
@@ -23234,7 +23246,7 @@
       </c>
       <c r="C12" s="41">
         <f t="array" aca="1" ref="C12" ca="1">_xlfn.IFNA(_xlfn.XLOOKUP($A12,INDIRECT("'"&amp;C$4&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;C$4&amp;"'!$b$10:$b$44"))," ")</f>
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D12" s="41" t="str">
         <f t="array" aca="1" ref="D12" ca="1">_xlfn.IFNA(_xlfn.XLOOKUP($A12,INDIRECT("'"&amp;D$4&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;D$4&amp;"'!$b$10:$b$44"))," ")</f>
@@ -23294,27 +23306,27 @@
       </c>
       <c r="T12" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="U12" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="V12" s="41">
         <f t="shared" ca="1" si="2"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="W12" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="X12" s="41">
         <f ca="1">RANK(T12,$T$5:$T$39)+COUNTIF($T$5:T12,T12)-1</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y12" s="34">
         <f t="array" aca="1" ref="Y12" ca="1">IFERROR(T12/SUMPRODUCT(($B12:$C12&lt;&gt;"")*$B$3:$C$3),0)</f>
-        <v>0.78125</v>
+        <v>0.71875</v>
       </c>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.3">
@@ -23327,7 +23339,7 @@
       </c>
       <c r="C13" s="41">
         <f t="array" aca="1" ref="C13" ca="1">_xlfn.IFNA(_xlfn.XLOOKUP($A13,INDIRECT("'"&amp;C$4&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;C$4&amp;"'!$b$10:$b$44"))," ")</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D13" s="41" t="str">
         <f t="array" aca="1" ref="D13" ca="1">_xlfn.IFNA(_xlfn.XLOOKUP($A13,INDIRECT("'"&amp;D$4&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;D$4&amp;"'!$b$10:$b$44"))," ")</f>
@@ -23387,11 +23399,11 @@
       </c>
       <c r="T13" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="U13" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="V13" s="41">
         <f t="shared" ca="1" si="2"/>
@@ -23399,15 +23411,15 @@
       </c>
       <c r="W13" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="X13" s="41">
         <f ca="1">RANK(T13,$T$5:$T$39)+COUNTIF($T$5:T13,T13)-1</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Y13" s="34">
         <f t="array" aca="1" ref="Y13" ca="1">IFERROR(T13/SUMPRODUCT(($B13:$C13&lt;&gt;"")*$B$3:$C$3),0)</f>
-        <v>0.6875</v>
+        <v>0.65625</v>
       </c>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.3">
@@ -23420,7 +23432,7 @@
       </c>
       <c r="C14" s="41">
         <f t="array" aca="1" ref="C14" ca="1">_xlfn.IFNA(_xlfn.XLOOKUP($A14,INDIRECT("'"&amp;C$4&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;C$4&amp;"'!$b$10:$b$44"))," ")</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D14" s="41" t="str">
         <f t="array" aca="1" ref="D14" ca="1">_xlfn.IFNA(_xlfn.XLOOKUP($A14,INDIRECT("'"&amp;D$4&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;D$4&amp;"'!$b$10:$b$44"))," ")</f>
@@ -23480,15 +23492,15 @@
       </c>
       <c r="T14" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="U14" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="V14" s="41">
         <f t="shared" ca="1" si="2"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="W14" s="41">
         <f t="shared" ca="1" si="3"/>
@@ -23496,11 +23508,11 @@
       </c>
       <c r="X14" s="41">
         <f ca="1">RANK(T14,$T$5:$T$39)+COUNTIF($T$5:T14,T14)-1</f>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Y14" s="34">
         <f t="array" aca="1" ref="Y14" ca="1">IFERROR(T14/SUMPRODUCT(($B14:$C14&lt;&gt;"")*$B$3:$C$3),0)</f>
-        <v>0.65625</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.3">
@@ -23589,7 +23601,7 @@
       </c>
       <c r="X15" s="41">
         <f ca="1">RANK(T15,$T$5:$T$39)+COUNTIF($T$5:T15,T15)-1</f>
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="Y15" s="34">
         <f t="array" aca="1" ref="Y15" ca="1">IFERROR(T15/SUMPRODUCT(($B15:$C15&lt;&gt;"")*$B$3:$C$3),0)</f>
@@ -23606,7 +23618,7 @@
       </c>
       <c r="C16" s="41">
         <f t="array" aca="1" ref="C16" ca="1">_xlfn.IFNA(_xlfn.XLOOKUP($A16,INDIRECT("'"&amp;C$4&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;C$4&amp;"'!$b$10:$b$44"))," ")</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D16" s="41" t="str">
         <f t="array" aca="1" ref="D16" ca="1">_xlfn.IFNA(_xlfn.XLOOKUP($A16,INDIRECT("'"&amp;D$4&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;D$4&amp;"'!$b$10:$b$44"))," ")</f>
@@ -23666,11 +23678,11 @@
       </c>
       <c r="T16" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="U16" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="V16" s="41">
         <f t="shared" ca="1" si="2"/>
@@ -23678,15 +23690,15 @@
       </c>
       <c r="W16" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="X16" s="41">
         <f ca="1">RANK(T16,$T$5:$T$39)+COUNTIF($T$5:T16,T16)-1</f>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y16" s="34">
         <f t="array" aca="1" ref="Y16" ca="1">IFERROR(T16/SUMPRODUCT(($B16:$C16&lt;&gt;"")*$B$3:$C$3),0)</f>
-        <v>0.71875</v>
+        <v>0.6875</v>
       </c>
     </row>
     <row r="17" spans="1:25" x14ac:dyDescent="0.3">
@@ -23699,7 +23711,7 @@
       </c>
       <c r="C17" s="41">
         <f t="array" aca="1" ref="C17" ca="1">_xlfn.IFNA(_xlfn.XLOOKUP($A17,INDIRECT("'"&amp;C$4&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;C$4&amp;"'!$b$10:$b$44"))," ")</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D17" s="41" t="str">
         <f t="array" aca="1" ref="D17" ca="1">_xlfn.IFNA(_xlfn.XLOOKUP($A17,INDIRECT("'"&amp;D$4&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;D$4&amp;"'!$b$10:$b$44"))," ")</f>
@@ -23759,11 +23771,11 @@
       </c>
       <c r="T17" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="U17" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="V17" s="41">
         <f t="shared" ca="1" si="2"/>
@@ -23771,15 +23783,15 @@
       </c>
       <c r="W17" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X17" s="41">
         <f ca="1">RANK(T17,$T$5:$T$39)+COUNTIF($T$5:T17,T17)-1</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Y17" s="34">
         <f t="array" aca="1" ref="Y17" ca="1">IFERROR(T17/SUMPRODUCT(($B17:$C17&lt;&gt;"")*$B$3:$C$3),0)</f>
-        <v>0.6875</v>
+        <v>0.65625</v>
       </c>
     </row>
     <row r="18" spans="1:25" x14ac:dyDescent="0.3">
@@ -23792,7 +23804,7 @@
       </c>
       <c r="C18" s="41">
         <f t="array" aca="1" ref="C18" ca="1">_xlfn.IFNA(_xlfn.XLOOKUP($A18,INDIRECT("'"&amp;C$4&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;C$4&amp;"'!$b$10:$b$44"))," ")</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D18" s="41" t="str">
         <f t="array" aca="1" ref="D18" ca="1">_xlfn.IFNA(_xlfn.XLOOKUP($A18,INDIRECT("'"&amp;D$4&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;D$4&amp;"'!$b$10:$b$44"))," ")</f>
@@ -23852,11 +23864,11 @@
       </c>
       <c r="T18" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="U18" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="V18" s="41">
         <f t="shared" ca="1" si="2"/>
@@ -23864,7 +23876,7 @@
       </c>
       <c r="W18" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X18" s="41">
         <f ca="1">RANK(T18,$T$5:$T$39)+COUNTIF($T$5:T18,T18)-1</f>
@@ -23872,7 +23884,7 @@
       </c>
       <c r="Y18" s="34">
         <f t="array" aca="1" ref="Y18" ca="1">IFERROR(T18/SUMPRODUCT(($B18:$C18&lt;&gt;"")*$B$3:$C$3),0)</f>
-        <v>0.5</v>
+        <v>0.46875</v>
       </c>
     </row>
     <row r="19" spans="1:25" x14ac:dyDescent="0.3">
@@ -23885,7 +23897,7 @@
       </c>
       <c r="C19" s="41">
         <f t="array" aca="1" ref="C19" ca="1">_xlfn.IFNA(_xlfn.XLOOKUP($A19,INDIRECT("'"&amp;C$4&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;C$4&amp;"'!$b$10:$b$44"))," ")</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D19" s="41" t="str">
         <f t="array" aca="1" ref="D19" ca="1">_xlfn.IFNA(_xlfn.XLOOKUP($A19,INDIRECT("'"&amp;D$4&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;D$4&amp;"'!$b$10:$b$44"))," ")</f>
@@ -23945,15 +23957,15 @@
       </c>
       <c r="T19" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="U19" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="V19" s="41">
         <f t="shared" ca="1" si="2"/>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="W19" s="41">
         <f t="shared" ca="1" si="3"/>
@@ -23965,7 +23977,7 @@
       </c>
       <c r="Y19" s="34">
         <f t="array" aca="1" ref="Y19" ca="1">IFERROR(T19/SUMPRODUCT(($B19:$C19&lt;&gt;"")*$B$3:$C$3),0)</f>
-        <v>0.875</v>
+        <v>0.84375</v>
       </c>
     </row>
     <row r="20" spans="1:25" x14ac:dyDescent="0.3">
@@ -23978,7 +23990,7 @@
       </c>
       <c r="C20" s="41">
         <f t="array" aca="1" ref="C20" ca="1">_xlfn.IFNA(_xlfn.XLOOKUP($A20,INDIRECT("'"&amp;C$4&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;C$4&amp;"'!$b$10:$b$44"))," ")</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D20" s="41" t="str">
         <f t="array" aca="1" ref="D20" ca="1">_xlfn.IFNA(_xlfn.XLOOKUP($A20,INDIRECT("'"&amp;D$4&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;D$4&amp;"'!$b$10:$b$44"))," ")</f>
@@ -24038,11 +24050,11 @@
       </c>
       <c r="T20" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="U20" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="V20" s="41">
         <f t="shared" ca="1" si="2"/>
@@ -24050,15 +24062,15 @@
       </c>
       <c r="W20" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X20" s="41">
         <f ca="1">RANK(T20,$T$5:$T$39)+COUNTIF($T$5:T20,T20)-1</f>
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Y20" s="34">
         <f t="array" aca="1" ref="Y20" ca="1">IFERROR(T20/SUMPRODUCT(($B20:$C20&lt;&gt;"")*$B$3:$C$3),0)</f>
-        <v>0.625</v>
+        <v>0.59375</v>
       </c>
     </row>
     <row r="21" spans="1:25" x14ac:dyDescent="0.3">
@@ -24071,7 +24083,7 @@
       </c>
       <c r="C21" s="41">
         <f t="array" aca="1" ref="C21" ca="1">_xlfn.IFNA(_xlfn.XLOOKUP($A21,INDIRECT("'"&amp;C$4&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;C$4&amp;"'!$b$10:$b$44"))," ")</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D21" s="41" t="str">
         <f t="array" aca="1" ref="D21" ca="1">_xlfn.IFNA(_xlfn.XLOOKUP($A21,INDIRECT("'"&amp;D$4&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;D$4&amp;"'!$b$10:$b$44"))," ")</f>
@@ -24131,11 +24143,11 @@
       </c>
       <c r="T21" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="U21" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="V21" s="41">
         <f t="shared" ca="1" si="2"/>
@@ -24143,15 +24155,15 @@
       </c>
       <c r="W21" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X21" s="41">
         <f ca="1">RANK(T21,$T$5:$T$39)+COUNTIF($T$5:T21,T21)-1</f>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y21" s="34">
         <f t="array" aca="1" ref="Y21" ca="1">IFERROR(T21/SUMPRODUCT(($B21:$C21&lt;&gt;"")*$B$3:$C$3),0)</f>
-        <v>0.65625</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="22" spans="1:25" x14ac:dyDescent="0.3">
@@ -24240,7 +24252,7 @@
       </c>
       <c r="X22" s="41">
         <f ca="1">RANK(T22,$T$5:$T$39)+COUNTIF($T$5:T22,T22)-1</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Y22" s="34">
         <f t="array" aca="1" ref="Y22" ca="1">IFERROR(T22/SUMPRODUCT(($B22:$C22&lt;&gt;"")*$B$3:$C$3),0)</f>
@@ -24257,7 +24269,7 @@
       </c>
       <c r="C23" s="41">
         <f t="array" aca="1" ref="C23" ca="1">_xlfn.IFNA(_xlfn.XLOOKUP($A23,INDIRECT("'"&amp;C$4&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;C$4&amp;"'!$b$10:$b$44"))," ")</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D23" s="41" t="str">
         <f t="array" aca="1" ref="D23" ca="1">_xlfn.IFNA(_xlfn.XLOOKUP($A23,INDIRECT("'"&amp;D$4&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;D$4&amp;"'!$b$10:$b$44"))," ")</f>
@@ -24317,15 +24329,15 @@
       </c>
       <c r="T23" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="U23" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="V23" s="41">
         <f t="shared" ca="1" si="2"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="W23" s="41">
         <f t="shared" ca="1" si="3"/>
@@ -24333,11 +24345,11 @@
       </c>
       <c r="X23" s="41">
         <f ca="1">RANK(T23,$T$5:$T$39)+COUNTIF($T$5:T23,T23)-1</f>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Y23" s="34">
         <f t="array" aca="1" ref="Y23" ca="1">IFERROR(T23/SUMPRODUCT(($B23:$C23&lt;&gt;"")*$B$3:$C$3),0)</f>
-        <v>0.59375</v>
+        <v>0.5625</v>
       </c>
     </row>
     <row r="24" spans="1:25" x14ac:dyDescent="0.3">
@@ -24350,7 +24362,7 @@
       </c>
       <c r="C24" s="41">
         <f t="array" aca="1" ref="C24" ca="1">_xlfn.IFNA(_xlfn.XLOOKUP($A24,INDIRECT("'"&amp;C$4&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;C$4&amp;"'!$b$10:$b$44"))," ")</f>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D24" s="41" t="str">
         <f t="array" aca="1" ref="D24" ca="1">_xlfn.IFNA(_xlfn.XLOOKUP($A24,INDIRECT("'"&amp;D$4&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;D$4&amp;"'!$b$10:$b$44"))," ")</f>
@@ -24410,27 +24422,27 @@
       </c>
       <c r="T24" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="U24" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="V24" s="41">
         <f t="shared" ca="1" si="2"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="W24" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="X24" s="41">
         <f ca="1">RANK(T24,$T$5:$T$39)+COUNTIF($T$5:T24,T24)-1</f>
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="Y24" s="34">
         <f t="array" aca="1" ref="Y24" ca="1">IFERROR(T24/SUMPRODUCT(($B24:$C24&lt;&gt;"")*$B$3:$C$3),0)</f>
-        <v>0.71875</v>
+        <v>0.65625</v>
       </c>
     </row>
     <row r="25" spans="1:25" x14ac:dyDescent="0.3">
@@ -24521,7 +24533,7 @@
       </c>
       <c r="X25" s="26">
         <f ca="1">RANK(T25,$T$5:$T$39)+COUNTIF($T$5:T25,T25)-1</f>
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y25" s="34">
         <f t="array" aca="1" ref="Y25" ca="1">IFERROR(T25/SUMPRODUCT(($B25:$C25&lt;&gt;"")*$B$3:$C$3),0)</f>
@@ -24538,7 +24550,7 @@
       </c>
       <c r="C26" s="26">
         <f t="array" aca="1" ref="C26" ca="1">_xlfn.IFNA(_xlfn.XLOOKUP($A26,INDIRECT("'"&amp;C$4&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;C$4&amp;"'!$b$10:$b$44"))," ")</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D26" s="26" t="str">
         <f t="array" aca="1" ref="D26" ca="1">_xlfn.IFNA(_xlfn.XLOOKUP($A26,INDIRECT("'"&amp;D$4&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;D$4&amp;"'!$b$10:$b$44"))," ")</f>
@@ -24600,11 +24612,11 @@
       <c r="S26" s="26"/>
       <c r="T26" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="U26" s="27">
         <f t="shared" ca="1" si="1"/>
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="V26" s="26">
         <f t="shared" ca="1" si="2"/>
@@ -24612,15 +24624,15 @@
       </c>
       <c r="W26" s="26">
         <f t="shared" ca="1" si="3"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="X26" s="26">
         <f ca="1">RANK(T26,$T$5:$T$39)+COUNTIF($T$5:T26,T26)-1</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y26" s="34">
         <f t="array" aca="1" ref="Y26" ca="1">IFERROR(T26/SUMPRODUCT(($B26:$C26&lt;&gt;"")*$B$3:$C$3),0)</f>
-        <v>0.78125</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="27" spans="1:25" x14ac:dyDescent="0.3">
@@ -24633,7 +24645,7 @@
       </c>
       <c r="C27" s="41">
         <f t="array" aca="1" ref="C27" ca="1">_xlfn.IFNA(_xlfn.XLOOKUP($A27,INDIRECT("'"&amp;C$4&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;C$4&amp;"'!$b$10:$b$44"))," ")</f>
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D27" s="41" t="str">
         <f t="array" aca="1" ref="D27" ca="1">_xlfn.IFNA(_xlfn.XLOOKUP($A27,INDIRECT("'"&amp;D$4&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;D$4&amp;"'!$b$10:$b$44"))," ")</f>
@@ -24693,27 +24705,27 @@
       </c>
       <c r="T27" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="U27" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="V27" s="41">
         <f t="shared" ca="1" si="2"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="W27" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="X27" s="41">
         <f ca="1">RANK(T27,$T$5:$T$39)+COUNTIF($T$5:T27,T27)-1</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y27" s="34">
         <f t="array" aca="1" ref="Y27" ca="1">IFERROR(T27/SUMPRODUCT(($B27:$C27&lt;&gt;"")*$B$3:$C$3),0)</f>
-        <v>0.78125</v>
+        <v>0.71875</v>
       </c>
     </row>
     <row r="28" spans="1:25" x14ac:dyDescent="0.3">
@@ -24726,7 +24738,7 @@
       </c>
       <c r="C28" s="41">
         <f t="array" aca="1" ref="C28" ca="1">_xlfn.IFNA(_xlfn.XLOOKUP($A28,INDIRECT("'"&amp;C$4&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;C$4&amp;"'!$b$10:$b$44"))," ")</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D28" s="41" t="str">
         <f t="array" aca="1" ref="D28" ca="1">_xlfn.IFNA(_xlfn.XLOOKUP($A28,INDIRECT("'"&amp;D$4&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;D$4&amp;"'!$b$10:$b$44"))," ")</f>
@@ -24786,15 +24798,15 @@
       </c>
       <c r="T28" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="U28" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="V28" s="41">
         <f t="shared" ca="1" si="2"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="W28" s="41">
         <f t="shared" ca="1" si="3"/>
@@ -24802,11 +24814,11 @@
       </c>
       <c r="X28" s="41">
         <f ca="1">RANK(T28,$T$5:$T$39)+COUNTIF($T$5:T28,T28)-1</f>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Y28" s="34">
         <f t="array" aca="1" ref="Y28" ca="1">IFERROR(T28/SUMPRODUCT(($B28:$C28&lt;&gt;"")*$B$3:$C$3),0)</f>
-        <v>0.59375</v>
+        <v>0.5625</v>
       </c>
     </row>
     <row r="29" spans="1:25" x14ac:dyDescent="0.3">
@@ -24819,7 +24831,7 @@
       </c>
       <c r="C29" s="41">
         <f t="array" aca="1" ref="C29" ca="1">_xlfn.IFNA(_xlfn.XLOOKUP($A29,INDIRECT("'"&amp;C$4&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;C$4&amp;"'!$b$10:$b$44"))," ")</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D29" s="41" t="str">
         <f t="array" aca="1" ref="D29" ca="1">_xlfn.IFNA(_xlfn.XLOOKUP($A29,INDIRECT("'"&amp;D$4&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;D$4&amp;"'!$b$10:$b$44"))," ")</f>
@@ -24879,11 +24891,11 @@
       </c>
       <c r="T29" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="U29" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V29" s="41">
         <f t="shared" ca="1" si="2"/>
@@ -24891,15 +24903,15 @@
       </c>
       <c r="W29" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="X29" s="41">
         <f ca="1">RANK(T29,$T$5:$T$39)+COUNTIF($T$5:T29,T29)-1</f>
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Y29" s="34">
         <f t="array" aca="1" ref="Y29" ca="1">IFERROR(T29/SUMPRODUCT(($B29:$C29&lt;&gt;"")*$B$3:$C$3),0)</f>
-        <v>0.5625</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="30" spans="1:25" x14ac:dyDescent="0.3">
@@ -24912,7 +24924,7 @@
       </c>
       <c r="C30" s="41">
         <f t="array" aca="1" ref="C30" ca="1">_xlfn.IFNA(_xlfn.XLOOKUP($A30,INDIRECT("'"&amp;C$4&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;C$4&amp;"'!$b$10:$b$44"))," ")</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D30" s="41" t="str">
         <f t="array" aca="1" ref="D30" ca="1">_xlfn.IFNA(_xlfn.XLOOKUP($A30,INDIRECT("'"&amp;D$4&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;D$4&amp;"'!$b$10:$b$44"))," ")</f>
@@ -24972,15 +24984,15 @@
       </c>
       <c r="T30" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="U30" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="V30" s="41">
         <f t="shared" ca="1" si="2"/>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="W30" s="41">
         <f t="shared" ca="1" si="3"/>
@@ -24992,7 +25004,7 @@
       </c>
       <c r="Y30" s="34">
         <f t="array" aca="1" ref="Y30" ca="1">IFERROR(T30/SUMPRODUCT(($B30:$C30&lt;&gt;"")*$B$3:$C$3),0)</f>
-        <v>0.8125</v>
+        <v>0.78125</v>
       </c>
     </row>
     <row r="31" spans="1:25" x14ac:dyDescent="0.3">
@@ -25005,7 +25017,7 @@
       </c>
       <c r="C31" s="26">
         <f t="array" aca="1" ref="C31" ca="1">_xlfn.IFNA(_xlfn.XLOOKUP($A31,INDIRECT("'"&amp;C$4&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;C$4&amp;"'!$b$10:$b$44"))," ")</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D31" s="26" t="str">
         <f t="array" aca="1" ref="D31" ca="1">_xlfn.IFNA(_xlfn.XLOOKUP($A31,INDIRECT("'"&amp;D$4&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;D$4&amp;"'!$b$10:$b$44"))," ")</f>
@@ -25067,15 +25079,15 @@
       <c r="S31" s="26"/>
       <c r="T31" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="U31" s="27">
         <f t="shared" ca="1" si="1"/>
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="V31" s="26">
         <f t="shared" ca="1" si="2"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="W31" s="26">
         <f t="shared" ca="1" si="3"/>
@@ -25083,11 +25095,11 @@
       </c>
       <c r="X31" s="26">
         <f ca="1">RANK(T31,$T$5:$T$39)+COUNTIF($T$5:T31,T31)-1</f>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y31" s="34">
         <f t="array" aca="1" ref="Y31" ca="1">IFERROR(T31/SUMPRODUCT(($B31:$C31&lt;&gt;"")*$B$3:$C$3),0)</f>
-        <v>0.65625</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="32" spans="1:25" x14ac:dyDescent="0.3">
@@ -25100,7 +25112,7 @@
       </c>
       <c r="C32" s="41">
         <f t="array" aca="1" ref="C32" ca="1">_xlfn.IFNA(_xlfn.XLOOKUP($A32,INDIRECT("'"&amp;C$4&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;C$4&amp;"'!$b$10:$b$44"))," ")</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D32" s="41" t="str">
         <f t="array" aca="1" ref="D32" ca="1">_xlfn.IFNA(_xlfn.XLOOKUP($A32,INDIRECT("'"&amp;D$4&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;D$4&amp;"'!$b$10:$b$44"))," ")</f>
@@ -25160,15 +25172,15 @@
       </c>
       <c r="T32" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="U32" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="V32" s="41">
         <f t="shared" ca="1" si="2"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="W32" s="41">
         <f t="shared" ca="1" si="3"/>
@@ -25180,7 +25192,7 @@
       </c>
       <c r="Y32" s="34">
         <f t="array" aca="1" ref="Y32" ca="1">IFERROR(T32/SUMPRODUCT(($B32:$C32&lt;&gt;"")*$B$3:$C$3),0)</f>
-        <v>0.6875</v>
+        <v>0.65625</v>
       </c>
     </row>
     <row r="33" spans="1:25" x14ac:dyDescent="0.3">
@@ -25193,7 +25205,7 @@
       </c>
       <c r="C33" s="41">
         <f t="array" aca="1" ref="C33" ca="1">_xlfn.IFNA(_xlfn.XLOOKUP($A33,INDIRECT("'"&amp;C$4&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;C$4&amp;"'!$b$10:$b$44"))," ")</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D33" s="41" t="str">
         <f t="array" aca="1" ref="D33" ca="1">_xlfn.IFNA(_xlfn.XLOOKUP($A33,INDIRECT("'"&amp;D$4&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;D$4&amp;"'!$b$10:$b$44"))," ")</f>
@@ -25253,11 +25265,11 @@
       </c>
       <c r="T33" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="U33" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="V33" s="41">
         <f t="shared" ca="1" si="2"/>
@@ -25265,7 +25277,7 @@
       </c>
       <c r="W33" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="X33" s="41">
         <f ca="1">RANK(T33,$T$5:$T$39)+COUNTIF($T$5:T33,T33)-1</f>
@@ -25273,7 +25285,7 @@
       </c>
       <c r="Y33" s="34">
         <f t="array" aca="1" ref="Y33" ca="1">IFERROR(T33/SUMPRODUCT(($B33:$C33&lt;&gt;"")*$B$3:$C$3),0)</f>
-        <v>0.6875</v>
+        <v>0.65625</v>
       </c>
     </row>
     <row r="34" spans="1:25" x14ac:dyDescent="0.3">
@@ -25286,7 +25298,7 @@
       </c>
       <c r="C34" s="41">
         <f t="array" aca="1" ref="C34" ca="1">_xlfn.IFNA(_xlfn.XLOOKUP($A34,INDIRECT("'"&amp;C$4&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;C$4&amp;"'!$b$10:$b$44"))," ")</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D34" s="41" t="str">
         <f t="array" aca="1" ref="D34" ca="1">_xlfn.IFNA(_xlfn.XLOOKUP($A34,INDIRECT("'"&amp;D$4&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;D$4&amp;"'!$b$10:$b$44"))," ")</f>
@@ -25346,11 +25358,11 @@
       </c>
       <c r="T34" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="U34" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="V34" s="41">
         <f t="shared" ca="1" si="2"/>
@@ -25358,7 +25370,7 @@
       </c>
       <c r="W34" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X34" s="41">
         <f ca="1">RANK(T34,$T$5:$T$39)+COUNTIF($T$5:T34,T34)-1</f>
@@ -25366,7 +25378,7 @@
       </c>
       <c r="Y34" s="34">
         <f t="array" aca="1" ref="Y34" ca="1">IFERROR(T34/SUMPRODUCT(($B34:$C34&lt;&gt;"")*$B$3:$C$3),0)</f>
-        <v>0.6875</v>
+        <v>0.65625</v>
       </c>
     </row>
     <row r="35" spans="1:25" x14ac:dyDescent="0.3">
@@ -25379,7 +25391,7 @@
       </c>
       <c r="C35" s="41">
         <f t="array" aca="1" ref="C35" ca="1">_xlfn.IFNA(_xlfn.XLOOKUP($A35,INDIRECT("'"&amp;C$4&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;C$4&amp;"'!$b$10:$b$44"))," ")</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D35" s="41" t="str">
         <f t="array" aca="1" ref="D35" ca="1">_xlfn.IFNA(_xlfn.XLOOKUP($A35,INDIRECT("'"&amp;D$4&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;D$4&amp;"'!$b$10:$b$44"))," ")</f>
@@ -25439,15 +25451,15 @@
       </c>
       <c r="T35" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="U35" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="V35" s="41">
         <f t="shared" ca="1" si="2"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W35" s="41">
         <f t="shared" ca="1" si="3"/>
@@ -25455,11 +25467,11 @@
       </c>
       <c r="X35" s="41">
         <f ca="1">RANK(T35,$T$5:$T$39)+COUNTIF($T$5:T35,T35)-1</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Y35" s="34">
         <f t="array" aca="1" ref="Y35" ca="1">IFERROR(T35/SUMPRODUCT(($B35:$C35&lt;&gt;"")*$B$3:$C$3),0)</f>
-        <v>0.59375</v>
+        <v>0.5625</v>
       </c>
     </row>
     <row r="36" spans="1:25" x14ac:dyDescent="0.3">
@@ -25472,7 +25484,7 @@
       </c>
       <c r="C36" s="41">
         <f t="array" aca="1" ref="C36" ca="1">_xlfn.IFNA(_xlfn.XLOOKUP($A36,INDIRECT("'"&amp;C$4&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;C$4&amp;"'!$b$10:$b$44"))," ")</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D36" s="41" t="str">
         <f t="array" aca="1" ref="D36" ca="1">_xlfn.IFNA(_xlfn.XLOOKUP($A36,INDIRECT("'"&amp;D$4&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;D$4&amp;"'!$b$10:$b$44"))," ")</f>
@@ -25532,11 +25544,11 @@
       </c>
       <c r="T36" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="U36" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="V36" s="41">
         <f t="shared" ca="1" si="2"/>
@@ -25544,15 +25556,15 @@
       </c>
       <c r="W36" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X36" s="41">
         <f ca="1">RANK(T36,$T$5:$T$39)+COUNTIF($T$5:T36,T36)-1</f>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Y36" s="34">
         <f t="array" aca="1" ref="Y36" ca="1">IFERROR(T36/SUMPRODUCT(($B36:$C36&lt;&gt;"")*$B$3:$C$3),0)</f>
-        <v>0.5625</v>
+        <v>0.53125</v>
       </c>
     </row>
     <row r="37" spans="1:25" x14ac:dyDescent="0.3">
@@ -25565,7 +25577,7 @@
       </c>
       <c r="C37" s="26">
         <f t="array" aca="1" ref="C37" ca="1">_xlfn.IFNA(_xlfn.XLOOKUP($A37,INDIRECT("'"&amp;C$4&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;C$4&amp;"'!$b$10:$b$44"))," ")</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D37" s="26" t="str">
         <f t="array" aca="1" ref="D37" ca="1">_xlfn.IFNA(_xlfn.XLOOKUP($A37,INDIRECT("'"&amp;D$4&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;D$4&amp;"'!$b$10:$b$44"))," ")</f>
@@ -25627,11 +25639,11 @@
       <c r="S37" s="26"/>
       <c r="T37" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="U37" s="27">
         <f t="shared" ca="1" si="1"/>
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="V37" s="26">
         <f t="shared" ca="1" si="2"/>
@@ -25639,15 +25651,15 @@
       </c>
       <c r="W37" s="26">
         <f t="shared" ca="1" si="3"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X37" s="26">
         <f ca="1">RANK(T37,$T$5:$T$39)+COUNTIF($T$5:T37,T37)-1</f>
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y37" s="34">
         <f t="array" aca="1" ref="Y37" ca="1">IFERROR(T37/SUMPRODUCT(($B37:$C37&lt;&gt;"")*$B$3:$C$3),0)</f>
-        <v>0.65625</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="38" spans="1:25" x14ac:dyDescent="0.3">
@@ -25660,7 +25672,7 @@
       </c>
       <c r="C38" s="41">
         <f t="array" aca="1" ref="C38" ca="1">_xlfn.IFNA(_xlfn.XLOOKUP($A38,INDIRECT("'"&amp;C$4&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;C$4&amp;"'!$b$10:$b$44"))," ")</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D38" s="41" t="str">
         <f t="array" aca="1" ref="D38" ca="1">_xlfn.IFNA(_xlfn.XLOOKUP($A38,INDIRECT("'"&amp;D$4&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;D$4&amp;"'!$b$10:$b$44"))," ")</f>
@@ -25720,15 +25732,15 @@
       </c>
       <c r="T38" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U38" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="V38" s="41">
         <f t="shared" ca="1" si="2"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="W38" s="41">
         <f t="shared" ca="1" si="3"/>
@@ -25736,11 +25748,11 @@
       </c>
       <c r="X38" s="41">
         <f ca="1">RANK(T38,$T$5:$T$39)+COUNTIF($T$5:T38,T38)-1</f>
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="Y38" s="34">
         <f t="array" aca="1" ref="Y38" ca="1">IFERROR(T38/SUMPRODUCT(($B38:$C38&lt;&gt;"")*$B$3:$C$3),0)</f>
-        <v>0.6875</v>
+        <v>0.71875</v>
       </c>
     </row>
     <row r="39" spans="1:25" x14ac:dyDescent="0.3">
@@ -25753,7 +25765,7 @@
       </c>
       <c r="C39" s="41">
         <f t="array" aca="1" ref="C39" ca="1">_xlfn.IFNA(_xlfn.XLOOKUP($A39,INDIRECT("'"&amp;C$4&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;C$4&amp;"'!$b$10:$b$44"))," ")</f>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D39" s="41" t="str">
         <f t="array" aca="1" ref="D39" ca="1">_xlfn.IFNA(_xlfn.XLOOKUP($A39,INDIRECT("'"&amp;D$4&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;D$4&amp;"'!$b$10:$b$44"))," ")</f>
@@ -25813,11 +25825,11 @@
       </c>
       <c r="T39" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="U39" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V39" s="41">
         <f t="shared" ca="1" si="2"/>
@@ -25825,15 +25837,15 @@
       </c>
       <c r="W39" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X39" s="41">
         <f ca="1">RANK(T39,$T$5:$T$39)+COUNTIF($T$5:T39,T39)-1</f>
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="Y39" s="34">
         <f t="array" aca="1" ref="Y39" ca="1">IFERROR(T39/SUMPRODUCT(($B39:$C39&lt;&gt;"")*$B$3:$C$3),0)</f>
-        <v>0.6875</v>
+        <v>0.625</v>
       </c>
     </row>
   </sheetData>
@@ -27333,7 +27345,7 @@
       </c>
       <c r="C19" s="30">
         <f t="array" aca="1" ref="C19" ca="1">_xlfn.IFNA(_xlfn.XLOOKUP($A19,INDIRECT("'"&amp;C$4&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;C$4&amp;"'!$A$10:$A$44"))," ")</f>
-        <v>150</v>
+        <v>75.5</v>
       </c>
       <c r="D19" s="30" t="str">
         <f t="array" aca="1" ref="D19" ca="1">_xlfn.IFNA(_xlfn.XLOOKUP($A19,INDIRECT("'"&amp;D$4&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;D$4&amp;"'!$A$10:$A$44"))," ")</f>
@@ -27401,19 +27413,19 @@
       </c>
       <c r="T19" s="30">
         <f ca="1">SUM(Table5[[#This Row],[Week 1]:[Week 18]])</f>
-        <v>150</v>
+        <v>75.5</v>
       </c>
       <c r="U19" s="30">
         <f t="shared" ca="1" si="0"/>
-        <v>110</v>
+        <v>35.5</v>
       </c>
       <c r="V19" s="30">
         <f t="shared" ca="1" si="1"/>
-        <v>150</v>
+        <v>75.5</v>
       </c>
       <c r="W19" s="30">
         <f t="shared" ca="1" si="2"/>
-        <v>150</v>
+        <v>75.5</v>
       </c>
     </row>
     <row r="20" spans="1:23" x14ac:dyDescent="0.3">
@@ -29098,9 +29110,9 @@
         <f t="array" aca="1" ref="B38" ca="1">_xlfn.IFNA(_xlfn.XLOOKUP($A38,INDIRECT("'"&amp;B$4&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;B$4&amp;"'!$A$10:$A$44"))," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="C38" s="30" t="str">
+      <c r="C38" s="30">
         <f t="array" aca="1" ref="C38" ca="1">_xlfn.IFNA(_xlfn.XLOOKUP($A38,INDIRECT("'"&amp;C$4&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;C$4&amp;"'!$A$10:$A$44"))," ")</f>
-        <v/>
+        <v>75.5</v>
       </c>
       <c r="D38" s="30" t="str">
         <f t="array" aca="1" ref="D38" ca="1">_xlfn.IFNA(_xlfn.XLOOKUP($A38,INDIRECT("'"&amp;D$4&amp;"'!$E$10:$E$44"),INDIRECT("'"&amp;D$4&amp;"'!$A$10:$A$44"))," ")</f>
@@ -29168,19 +29180,19 @@
       </c>
       <c r="T38" s="30">
         <f ca="1">SUM(Table5[[#This Row],[Week 1]:[Week 18]])</f>
-        <v>0</v>
+        <v>75.5</v>
       </c>
       <c r="U38" s="30">
         <f t="shared" ca="1" si="0"/>
-        <v>-40</v>
+        <v>35.5</v>
       </c>
       <c r="V38" s="30">
         <f t="shared" ca="1" si="1"/>
-        <v>0</v>
+        <v>75.5</v>
       </c>
       <c r="W38" s="30">
         <f t="shared" ca="1" si="2"/>
-        <v>0</v>
+        <v>75.5</v>
       </c>
     </row>
     <row r="39" spans="1:23" x14ac:dyDescent="0.3">
@@ -29286,7 +29298,7 @@
       </c>
       <c r="C40" s="31">
         <f ca="1">SUBTOTAL(104,Table5[Week 2])</f>
-        <v>150</v>
+        <v>75.5</v>
       </c>
       <c r="D40" s="31">
         <f ca="1">SUBTOTAL(104,Table5[Week 3])</f>
@@ -29354,19 +29366,19 @@
       </c>
       <c r="T40" s="31">
         <f ca="1">SUBTOTAL(109,Table5[Winning])</f>
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="U40" s="31">
         <f ca="1">SUBTOTAL(104,Table5[Total])</f>
-        <v>110</v>
+        <v>76</v>
       </c>
       <c r="V40" s="31">
         <f ca="1">SUBTOTAL(104,Table5[[Avg ]])</f>
-        <v>150</v>
+        <v>116</v>
       </c>
       <c r="W40" s="31">
         <f ca="1">SUBTOTAL(109,Table5[Best])</f>
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
   </sheetData>
@@ -32863,7 +32875,9 @@
       <c r="S6" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="T6" s="6"/>
+      <c r="T6" s="6" t="s">
+        <v>219</v>
+      </c>
       <c r="U6" s="6"/>
       <c r="V6" s="6"/>
       <c r="W6" s="6"/>
@@ -33066,11 +33080,11 @@
       </c>
       <c r="B10">
         <f t="shared" ref="B10:B44" si="2">SUM(V10:X10)+C10</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C10">
         <f t="shared" ref="C10:C44" si="3">COUNTA(F10:U10)</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D10">
         <f t="shared" ref="D10:D44" si="4">_xlfn.RANK.EQ(B10,$B$10:$B$44,0)</f>
@@ -33109,17 +33123,15 @@
         <v>235</v>
       </c>
       <c r="S10" s="36"/>
-      <c r="T10" s="37" t="s">
+      <c r="T10" s="37"/>
+      <c r="U10" s="35" t="s">
         <v>236</v>
-      </c>
-      <c r="U10" s="35" t="s">
-        <v>237</v>
       </c>
       <c r="V10" s="42" t="s">
         <v>163</v>
       </c>
       <c r="W10" s="42" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="X10" s="42">
         <v>1</v>
@@ -33136,7 +33148,7 @@
       </c>
       <c r="AB10" s="1">
         <f t="shared" ref="AB10:AB44" si="6">IFERROR(B10/16,0)</f>
-        <v>0.6875</v>
+        <v>0.625</v>
       </c>
       <c r="AD10" s="43">
         <f t="shared" ref="AD10:AD44" si="7">MAX($B$7:$B$141)-B10</f>
@@ -33150,15 +33162,15 @@
       </c>
       <c r="B11">
         <f t="shared" si="2"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C11">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D11">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E11" s="13" t="s">
         <v>59</v>
@@ -33180,13 +33192,13 @@
         <v>232</v>
       </c>
       <c r="L11" s="41" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="M11" s="41"/>
       <c r="N11" s="41"/>
       <c r="O11" s="41"/>
       <c r="P11" s="41" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q11" s="41" t="s">
         <v>234</v>
@@ -33195,11 +33207,9 @@
         <v>235</v>
       </c>
       <c r="S11" s="36"/>
-      <c r="T11" s="37" t="s">
+      <c r="T11" s="37"/>
+      <c r="U11" s="35" t="s">
         <v>236</v>
-      </c>
-      <c r="U11" s="35" t="s">
-        <v>237</v>
       </c>
       <c r="V11" s="42" t="s">
         <v>163</v>
@@ -33208,10 +33218,10 @@
         <v>1</v>
       </c>
       <c r="X11" s="42" t="s">
+        <v>240</v>
+      </c>
+      <c r="Y11" s="35" t="s">
         <v>241</v>
-      </c>
-      <c r="Y11" s="35" t="s">
-        <v>242</v>
       </c>
       <c r="Z11" s="1">
         <v>0.5625</v>
@@ -33222,7 +33232,7 @@
       </c>
       <c r="AB11" s="1">
         <f t="shared" si="6"/>
-        <v>0.75</v>
+        <v>0.6875</v>
       </c>
       <c r="AD11" s="43">
         <f t="shared" si="7"/>
@@ -33232,15 +33242,15 @@
     <row r="12" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <f t="shared" si="1"/>
-        <v>150</v>
+        <v>75.5</v>
       </c>
       <c r="B12">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C12">
         <f t="shared" si="3"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D12">
         <f t="shared" si="4"/>
@@ -33266,7 +33276,7 @@
         <v>232</v>
       </c>
       <c r="L12" s="41" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="M12" s="41" t="s">
         <v>167</v>
@@ -33276,7 +33286,7 @@
         <v>233</v>
       </c>
       <c r="P12" s="41" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q12" s="41" t="s">
         <v>234</v>
@@ -33286,11 +33296,9 @@
       </c>
       <c r="S12" s="36"/>
       <c r="T12" s="37" t="s">
-        <v>243</v>
-      </c>
-      <c r="U12" s="35" t="s">
-        <v>244</v>
-      </c>
+        <v>242</v>
+      </c>
+      <c r="U12" s="35"/>
       <c r="V12" s="42">
         <v>1</v>
       </c>
@@ -33312,7 +33320,7 @@
       </c>
       <c r="AB12" s="1">
         <f t="shared" si="6"/>
-        <v>0.9375</v>
+        <v>0.875</v>
       </c>
       <c r="AD12" s="43">
         <f t="shared" si="7"/>
@@ -33326,15 +33334,15 @@
       </c>
       <c r="B13">
         <f t="shared" si="2"/>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C13">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D13">
         <f t="shared" si="4"/>
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E13" s="13" t="s">
         <v>82</v>
@@ -33363,19 +33371,15 @@
       </c>
       <c r="R13" s="28"/>
       <c r="S13" s="36" t="s">
-        <v>245</v>
-      </c>
-      <c r="T13" s="37" t="s">
-        <v>236</v>
-      </c>
-      <c r="U13" s="35" t="s">
-        <v>244</v>
-      </c>
+        <v>243</v>
+      </c>
+      <c r="T13" s="37"/>
+      <c r="U13" s="35"/>
       <c r="V13" s="42" t="s">
         <v>182</v>
       </c>
       <c r="W13" s="42" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="X13" s="42">
         <v>1</v>
@@ -33388,15 +33392,15 @@
       </c>
       <c r="AA13">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB13" s="1">
         <f t="shared" si="6"/>
-        <v>0.5625</v>
+        <v>0.4375</v>
       </c>
       <c r="AD13" s="43">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:30" x14ac:dyDescent="0.3">
@@ -33406,15 +33410,15 @@
       </c>
       <c r="B14">
         <f t="shared" si="2"/>
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C14">
         <f t="shared" si="3"/>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D14">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E14" s="13" t="s">
         <v>60</v>
@@ -33434,7 +33438,7 @@
         <v>232</v>
       </c>
       <c r="L14" s="28" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="M14" s="28" t="s">
         <v>167</v>
@@ -33451,16 +33455,12 @@
         <v>235</v>
       </c>
       <c r="S14" s="36" t="s">
-        <v>245</v>
-      </c>
-      <c r="T14" s="37" t="s">
-        <v>236</v>
-      </c>
-      <c r="U14" s="35" t="s">
-        <v>244</v>
-      </c>
+        <v>243</v>
+      </c>
+      <c r="T14" s="37"/>
+      <c r="U14" s="35"/>
       <c r="V14" s="42" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="W14" s="42" t="s">
         <v>157</v>
@@ -33476,15 +33476,15 @@
       </c>
       <c r="AA14">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB14" s="1">
         <f t="shared" si="6"/>
-        <v>0.8125</v>
+        <v>0.6875</v>
       </c>
       <c r="AD14" s="43">
         <f t="shared" si="7"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:30" x14ac:dyDescent="0.3">
@@ -33494,15 +33494,15 @@
       </c>
       <c r="B15">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C15">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D15">
         <f t="shared" si="4"/>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E15" s="13" t="s">
         <v>78</v>
@@ -33524,7 +33524,7 @@
       <c r="N15" s="41"/>
       <c r="O15" s="41"/>
       <c r="P15" s="41" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q15" s="41" t="s">
         <v>234</v>
@@ -33533,14 +33533,12 @@
         <v>235</v>
       </c>
       <c r="S15" s="36" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="T15" s="37" t="s">
-        <v>243</v>
-      </c>
-      <c r="U15" s="35" t="s">
-        <v>244</v>
-      </c>
+        <v>242</v>
+      </c>
+      <c r="U15" s="35"/>
       <c r="V15" s="42">
         <v>1</v>
       </c>
@@ -33548,10 +33546,10 @@
         <v>182</v>
       </c>
       <c r="X15" s="42" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="Y15" s="35" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="Z15" s="1">
         <v>0.5625</v>
@@ -33562,7 +33560,7 @@
       </c>
       <c r="AB15" s="1">
         <f t="shared" si="6"/>
-        <v>0.625</v>
+        <v>0.5625</v>
       </c>
       <c r="AD15" s="43">
         <f t="shared" si="7"/>
@@ -33576,15 +33574,15 @@
       </c>
       <c r="B16">
         <f t="shared" si="2"/>
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16">
         <f t="shared" si="3"/>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D16">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E16" s="13" t="s">
         <v>72</v>
@@ -33608,29 +33606,25 @@
         <v>167</v>
       </c>
       <c r="N16" s="41" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="O16" s="41" t="s">
         <v>233</v>
       </c>
       <c r="P16" s="41" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q16" s="41"/>
       <c r="R16" s="41" t="s">
         <v>235</v>
       </c>
       <c r="S16" s="36" t="s">
-        <v>245</v>
-      </c>
-      <c r="T16" s="37" t="s">
-        <v>236</v>
-      </c>
-      <c r="U16" s="35" t="s">
-        <v>244</v>
-      </c>
+        <v>243</v>
+      </c>
+      <c r="T16" s="37"/>
+      <c r="U16" s="35"/>
       <c r="V16" s="42" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="W16" s="42" t="s">
         <v>182</v>
@@ -33639,22 +33633,22 @@
         <v>1</v>
       </c>
       <c r="Y16" s="35" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="Z16" s="1">
         <v>0.4375</v>
       </c>
       <c r="AA16">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB16" s="1">
         <f t="shared" si="6"/>
-        <v>0.8125</v>
+        <v>0.6875</v>
       </c>
       <c r="AD16" s="43">
         <f t="shared" si="7"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:30" x14ac:dyDescent="0.3">
@@ -33664,15 +33658,15 @@
       </c>
       <c r="B17">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C17">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D17">
         <f t="shared" si="4"/>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E17" s="13" t="s">
         <v>65</v>
@@ -33703,25 +33697,23 @@
         <v>235</v>
       </c>
       <c r="S17" s="36" t="s">
-        <v>245</v>
-      </c>
-      <c r="T17" s="37" t="s">
+        <v>243</v>
+      </c>
+      <c r="T17" s="37"/>
+      <c r="U17" s="35" t="s">
         <v>236</v>
       </c>
-      <c r="U17" s="35" t="s">
+      <c r="V17" s="42">
+        <v>1</v>
+      </c>
+      <c r="W17" s="42" t="s">
         <v>237</v>
-      </c>
-      <c r="V17" s="42">
-        <v>1</v>
-      </c>
-      <c r="W17" s="42" t="s">
-        <v>238</v>
       </c>
       <c r="X17" s="42" t="s">
         <v>163</v>
       </c>
       <c r="Y17" s="35" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="Z17" s="1">
         <v>0.6875</v>
@@ -33732,7 +33724,7 @@
       </c>
       <c r="AB17" s="1">
         <f t="shared" si="6"/>
-        <v>0.625</v>
+        <v>0.5625</v>
       </c>
       <c r="AD17" s="43">
         <f t="shared" si="7"/>
@@ -33746,11 +33738,11 @@
       </c>
       <c r="B18">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C18">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D18">
         <f t="shared" si="4"/>
@@ -33772,7 +33764,7 @@
       <c r="L18" s="28"/>
       <c r="M18" s="28"/>
       <c r="N18" s="28" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="O18" s="28" t="s">
         <v>233</v>
@@ -33781,20 +33773,18 @@
       <c r="Q18" s="28"/>
       <c r="R18" s="28"/>
       <c r="S18" s="36"/>
-      <c r="T18" s="37" t="s">
+      <c r="T18" s="37"/>
+      <c r="U18" s="35" t="s">
         <v>236</v>
       </c>
-      <c r="U18" s="35" t="s">
-        <v>237</v>
-      </c>
       <c r="V18" s="42" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="W18" s="42" t="s">
         <v>182</v>
       </c>
       <c r="X18" s="42" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="Y18" s="35" t="s">
         <v>183</v>
@@ -33808,7 +33798,7 @@
       </c>
       <c r="AB18" s="1">
         <f t="shared" si="6"/>
-        <v>0.375</v>
+        <v>0.3125</v>
       </c>
       <c r="AD18" s="43">
         <f t="shared" si="7"/>
@@ -33822,11 +33812,11 @@
       </c>
       <c r="B19">
         <f t="shared" si="2"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C19">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D19">
         <f t="shared" si="4"/>
@@ -33863,25 +33853,23 @@
         <v>235</v>
       </c>
       <c r="S19" s="36" t="s">
-        <v>245</v>
-      </c>
-      <c r="T19" s="37" t="s">
+        <v>243</v>
+      </c>
+      <c r="T19" s="37"/>
+      <c r="U19" s="35" t="s">
         <v>236</v>
       </c>
-      <c r="U19" s="35" t="s">
+      <c r="V19" s="42">
+        <v>1</v>
+      </c>
+      <c r="W19" s="42" t="s">
         <v>237</v>
-      </c>
-      <c r="V19" s="42">
-        <v>1</v>
-      </c>
-      <c r="W19" s="42" t="s">
-        <v>238</v>
       </c>
       <c r="X19" s="42" t="s">
         <v>182</v>
       </c>
       <c r="Y19" s="35" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="Z19" s="1">
         <v>0.75</v>
@@ -33892,7 +33880,7 @@
       </c>
       <c r="AB19" s="1">
         <f t="shared" si="6"/>
-        <v>0.6875</v>
+        <v>0.625</v>
       </c>
       <c r="AD19" s="43">
         <f t="shared" si="7"/>
@@ -33914,7 +33902,7 @@
       </c>
       <c r="D20">
         <f t="shared" si="4"/>
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E20" s="13" t="s">
         <v>19</v>
@@ -33938,7 +33926,7 @@
         <v>167</v>
       </c>
       <c r="N20" s="41" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="O20" s="41"/>
       <c r="P20" s="41"/>
@@ -33947,32 +33935,32 @@
         <v>235</v>
       </c>
       <c r="S20" s="36" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="T20" s="37" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="U20" s="35" t="s">
+        <v>236</v>
+      </c>
+      <c r="V20" s="42">
+        <v>1</v>
+      </c>
+      <c r="W20" s="42" t="s">
         <v>237</v>
-      </c>
-      <c r="V20" s="42">
-        <v>1</v>
-      </c>
-      <c r="W20" s="42" t="s">
-        <v>238</v>
       </c>
       <c r="X20" s="42" t="s">
         <v>182</v>
       </c>
       <c r="Y20" s="35" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="Z20" s="1">
         <v>0.4375</v>
       </c>
       <c r="AA20">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AB20" s="1">
         <f t="shared" si="6"/>
@@ -33980,7 +33968,7 @@
       </c>
       <c r="AD20" s="43">
         <f t="shared" si="7"/>
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:30" x14ac:dyDescent="0.3">
@@ -33990,15 +33978,15 @@
       </c>
       <c r="B21">
         <f t="shared" si="2"/>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C21">
         <f t="shared" si="3"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D21">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E21" s="13" t="s">
         <v>75</v>
@@ -34018,7 +34006,7 @@
         <v>232</v>
       </c>
       <c r="L21" s="41" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="M21" s="41" t="s">
         <v>167</v>
@@ -34028,7 +34016,7 @@
         <v>233</v>
       </c>
       <c r="P21" s="41" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q21" s="41" t="s">
         <v>234</v>
@@ -34037,14 +34025,12 @@
         <v>235</v>
       </c>
       <c r="S21" s="36" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="T21" s="37" t="s">
-        <v>243</v>
-      </c>
-      <c r="U21" s="35" t="s">
-        <v>244</v>
-      </c>
+        <v>242</v>
+      </c>
+      <c r="U21" s="35"/>
       <c r="V21" s="42">
         <v>1</v>
       </c>
@@ -34066,7 +34052,7 @@
       </c>
       <c r="AB21" s="1">
         <f t="shared" si="6"/>
-        <v>0.875</v>
+        <v>0.8125</v>
       </c>
       <c r="AD21" s="43">
         <f t="shared" si="7"/>
@@ -34080,15 +34066,15 @@
       </c>
       <c r="B22">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C22">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D22">
         <f t="shared" si="4"/>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E22" s="13" t="s">
         <v>68</v>
@@ -34119,16 +34105,14 @@
       </c>
       <c r="R22" s="41"/>
       <c r="S22" s="36" t="s">
-        <v>245</v>
-      </c>
-      <c r="T22" s="37" t="s">
+        <v>243</v>
+      </c>
+      <c r="T22" s="37"/>
+      <c r="U22" s="35" t="s">
         <v>236</v>
       </c>
-      <c r="U22" s="35" t="s">
+      <c r="V22" s="42" t="s">
         <v>237</v>
-      </c>
-      <c r="V22" s="42" t="s">
-        <v>238</v>
       </c>
       <c r="W22" s="42">
         <v>1</v>
@@ -34148,7 +34132,7 @@
       </c>
       <c r="AB22" s="1">
         <f t="shared" si="6"/>
-        <v>0.625</v>
+        <v>0.5625</v>
       </c>
       <c r="AD22" s="43">
         <f t="shared" si="7"/>
@@ -34162,15 +34146,15 @@
       </c>
       <c r="B23">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C23">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D23">
         <f t="shared" si="4"/>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E23" s="13" t="s">
         <v>20</v>
@@ -34201,13 +34185,11 @@
         <v>235</v>
       </c>
       <c r="S23" s="36" t="s">
-        <v>245</v>
-      </c>
-      <c r="T23" s="37" t="s">
+        <v>243</v>
+      </c>
+      <c r="T23" s="37"/>
+      <c r="U23" s="35" t="s">
         <v>236</v>
-      </c>
-      <c r="U23" s="35" t="s">
-        <v>237</v>
       </c>
       <c r="V23" s="42" t="s">
         <v>163</v>
@@ -34216,10 +34198,10 @@
         <v>1</v>
       </c>
       <c r="X23" s="42" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="Y23" s="35" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="Z23" s="1">
         <v>0.6875</v>
@@ -34230,7 +34212,7 @@
       </c>
       <c r="AB23" s="1">
         <f t="shared" si="6"/>
-        <v>0.625</v>
+        <v>0.5625</v>
       </c>
       <c r="AD23" s="43">
         <f t="shared" si="7"/>
@@ -34244,11 +34226,11 @@
       </c>
       <c r="B24">
         <f t="shared" si="2"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C24">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D24">
         <f t="shared" si="4"/>
@@ -34278,26 +34260,24 @@
         <v>233</v>
       </c>
       <c r="P24" s="41" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q24" s="41"/>
       <c r="R24" s="41" t="s">
         <v>235</v>
       </c>
       <c r="S24" s="36" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="T24" s="37" t="s">
-        <v>243</v>
-      </c>
-      <c r="U24" s="35" t="s">
-        <v>244</v>
-      </c>
+        <v>242</v>
+      </c>
+      <c r="U24" s="35"/>
       <c r="V24" s="42" t="s">
         <v>182</v>
       </c>
       <c r="W24" s="42" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="X24" s="42">
         <v>1</v>
@@ -34314,7 +34294,7 @@
       </c>
       <c r="AB24" s="1">
         <f t="shared" si="6"/>
-        <v>0.6875</v>
+        <v>0.625</v>
       </c>
       <c r="AD24" s="43">
         <f t="shared" si="7"/>
@@ -34328,15 +34308,15 @@
       </c>
       <c r="B25">
         <f t="shared" si="2"/>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C25">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D25">
         <f t="shared" si="4"/>
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E25" s="13" t="s">
         <v>56</v>
@@ -34362,23 +34342,19 @@
         <v>233</v>
       </c>
       <c r="P25" s="41" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q25" s="41" t="s">
         <v>234</v>
       </c>
       <c r="R25" s="41"/>
       <c r="S25" s="36" t="s">
-        <v>245</v>
-      </c>
-      <c r="T25" s="37" t="s">
-        <v>236</v>
-      </c>
-      <c r="U25" s="35" t="s">
-        <v>244</v>
-      </c>
+        <v>243</v>
+      </c>
+      <c r="T25" s="37"/>
+      <c r="U25" s="35"/>
       <c r="V25" s="42" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="W25" s="42">
         <v>1</v>
@@ -34387,22 +34363,22 @@
         <v>182</v>
       </c>
       <c r="Y25" s="35" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="Z25" s="1">
         <v>0.6875</v>
       </c>
       <c r="AA25">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AB25" s="1">
         <f t="shared" si="6"/>
-        <v>0.6875</v>
+        <v>0.5625</v>
       </c>
       <c r="AD25" s="43">
         <f t="shared" si="7"/>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:30" x14ac:dyDescent="0.3">
@@ -34412,15 +34388,15 @@
       </c>
       <c r="B26">
         <f t="shared" si="2"/>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C26">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D26">
         <f t="shared" si="4"/>
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E26" s="13" t="s">
         <v>58</v>
@@ -34444,7 +34420,7 @@
         <v>233</v>
       </c>
       <c r="P26" s="28" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q26" s="28" t="s">
         <v>234</v>
@@ -34453,14 +34429,10 @@
         <v>235</v>
       </c>
       <c r="S26" s="36"/>
-      <c r="T26" s="37" t="s">
-        <v>236</v>
-      </c>
-      <c r="U26" s="35" t="s">
+      <c r="T26" s="37"/>
+      <c r="U26" s="35"/>
+      <c r="V26" s="42" t="s">
         <v>244</v>
-      </c>
-      <c r="V26" s="42" t="s">
-        <v>246</v>
       </c>
       <c r="W26" s="42" t="s">
         <v>182</v>
@@ -34476,15 +34448,15 @@
       </c>
       <c r="AA26">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB26" s="1">
         <f t="shared" si="6"/>
-        <v>0.5625</v>
+        <v>0.4375</v>
       </c>
       <c r="AD26" s="43">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:30" x14ac:dyDescent="0.3">
@@ -34494,11 +34466,11 @@
       </c>
       <c r="B27">
         <f t="shared" si="2"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C27">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D27">
         <f t="shared" si="4"/>
@@ -34522,7 +34494,7 @@
       <c r="N27" s="41"/>
       <c r="O27" s="41"/>
       <c r="P27" s="41" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q27" s="41" t="s">
         <v>234</v>
@@ -34531,25 +34503,23 @@
         <v>235</v>
       </c>
       <c r="S27" s="36" t="s">
-        <v>245</v>
-      </c>
-      <c r="T27" s="37" t="s">
+        <v>243</v>
+      </c>
+      <c r="T27" s="37"/>
+      <c r="U27" s="35" t="s">
         <v>236</v>
       </c>
-      <c r="U27" s="35" t="s">
+      <c r="V27" s="42">
+        <v>1</v>
+      </c>
+      <c r="W27" s="42" t="s">
         <v>237</v>
-      </c>
-      <c r="V27" s="42">
-        <v>1</v>
-      </c>
-      <c r="W27" s="42" t="s">
-        <v>238</v>
       </c>
       <c r="X27" s="42" t="s">
         <v>185</v>
       </c>
       <c r="Y27" s="35" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="Z27" s="1">
         <v>0.5</v>
@@ -34560,7 +34530,7 @@
       </c>
       <c r="AB27" s="1">
         <f t="shared" si="6"/>
-        <v>0.5625</v>
+        <v>0.5</v>
       </c>
       <c r="AD27" s="43">
         <f t="shared" si="7"/>
@@ -34574,11 +34544,11 @@
       </c>
       <c r="B28">
         <f t="shared" si="2"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C28">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D28">
         <f t="shared" si="4"/>
@@ -34602,7 +34572,7 @@
         <v>232</v>
       </c>
       <c r="L28" s="41" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="M28" s="41" t="s">
         <v>167</v>
@@ -34612,24 +34582,22 @@
         <v>233</v>
       </c>
       <c r="P28" s="41" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q28" s="41"/>
       <c r="R28" s="41" t="s">
         <v>235</v>
       </c>
       <c r="S28" s="36"/>
-      <c r="T28" s="37" t="s">
+      <c r="T28" s="37"/>
+      <c r="U28" s="35" t="s">
         <v>236</v>
-      </c>
-      <c r="U28" s="35" t="s">
-        <v>237</v>
       </c>
       <c r="V28" s="42" t="s">
         <v>187</v>
       </c>
       <c r="W28" s="42" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="X28" s="42" t="s">
         <v>182</v>
@@ -34646,7 +34614,7 @@
       </c>
       <c r="AB28" s="1">
         <f t="shared" si="6"/>
-        <v>0.6875</v>
+        <v>0.625</v>
       </c>
       <c r="AD28" s="43">
         <f t="shared" si="7"/>
@@ -34664,11 +34632,11 @@
       </c>
       <c r="C29">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D29">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E29" s="13" t="s">
         <v>69</v>
@@ -34690,45 +34658,43 @@
       <c r="L29" s="28"/>
       <c r="M29" s="28"/>
       <c r="N29" s="28" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="O29" s="28" t="s">
         <v>233</v>
       </c>
       <c r="P29" s="28" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q29" s="28"/>
       <c r="R29" s="28" t="s">
         <v>235</v>
       </c>
       <c r="S29" s="36" t="s">
-        <v>245</v>
-      </c>
-      <c r="T29" s="37" t="s">
+        <v>243</v>
+      </c>
+      <c r="T29" s="37"/>
+      <c r="U29" s="35" t="s">
         <v>236</v>
       </c>
-      <c r="U29" s="35" t="s">
+      <c r="V29" s="42" t="s">
         <v>237</v>
       </c>
-      <c r="V29" s="42" t="s">
-        <v>238</v>
-      </c>
       <c r="W29" s="42">
         <v>1</v>
       </c>
-      <c r="X29" s="42" t="s">
-        <v>177</v>
+      <c r="X29" s="42">
+        <v>1</v>
       </c>
       <c r="Y29" s="35" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="Z29" s="1">
         <v>0.6875</v>
       </c>
       <c r="AA29">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB29" s="1">
         <f t="shared" si="6"/>
@@ -34736,7 +34702,7 @@
       </c>
       <c r="AD29" s="43">
         <f t="shared" si="7"/>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:30" x14ac:dyDescent="0.3">
@@ -34746,15 +34712,15 @@
       </c>
       <c r="B30">
         <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="C30">
+        <f t="shared" si="3"/>
+        <v>9</v>
+      </c>
+      <c r="D30">
+        <f t="shared" si="4"/>
         <v>12</v>
-      </c>
-      <c r="C30">
-        <f t="shared" si="3"/>
-        <v>11</v>
-      </c>
-      <c r="D30">
-        <f t="shared" si="4"/>
-        <v>6</v>
       </c>
       <c r="E30" s="13" t="s">
         <v>71</v>
@@ -34780,7 +34746,7 @@
         <v>233</v>
       </c>
       <c r="P30" s="28" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q30" s="28" t="s">
         <v>234</v>
@@ -34789,14 +34755,10 @@
         <v>235</v>
       </c>
       <c r="S30" s="36" t="s">
-        <v>245</v>
-      </c>
-      <c r="T30" s="37" t="s">
-        <v>236</v>
-      </c>
-      <c r="U30" s="35" t="s">
-        <v>244</v>
-      </c>
+        <v>243</v>
+      </c>
+      <c r="T30" s="37"/>
+      <c r="U30" s="35"/>
       <c r="V30" s="42" t="s">
         <v>163</v>
       </c>
@@ -34807,22 +34769,22 @@
         <v>182</v>
       </c>
       <c r="Y30" s="35" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="Z30" s="1">
         <v>0.625</v>
       </c>
       <c r="AA30">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB30" s="1">
         <f t="shared" si="6"/>
-        <v>0.75</v>
+        <v>0.625</v>
       </c>
       <c r="AD30" s="43">
         <f t="shared" si="7"/>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31" spans="1:30" x14ac:dyDescent="0.3">
@@ -34840,7 +34802,7 @@
       </c>
       <c r="D31">
         <f t="shared" si="4"/>
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E31" s="13" t="s">
         <v>63</v>
@@ -34860,39 +34822,39 @@
       <c r="N31" s="28"/>
       <c r="O31" s="28"/>
       <c r="P31" s="28" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q31" s="28" t="s">
         <v>234</v>
       </c>
       <c r="R31" s="28"/>
       <c r="S31" s="36" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="T31" s="37" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="U31" s="35" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="V31" s="42">
         <v>1</v>
       </c>
       <c r="W31" s="42" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="X31" s="42" t="s">
         <v>163</v>
       </c>
       <c r="Y31" s="35" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="Z31" s="1">
         <v>0.625</v>
       </c>
       <c r="AA31">
         <f t="shared" si="5"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB31" s="1">
         <f t="shared" si="6"/>
@@ -34900,7 +34862,7 @@
       </c>
       <c r="AD31" s="43">
         <f t="shared" si="7"/>
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32" spans="1:30" x14ac:dyDescent="0.3">
@@ -34910,11 +34872,11 @@
       </c>
       <c r="B32">
         <f t="shared" si="2"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C32">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D32">
         <f t="shared" si="4"/>
@@ -34938,11 +34900,11 @@
       <c r="L32" s="28"/>
       <c r="M32" s="28"/>
       <c r="N32" s="28" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="O32" s="28"/>
       <c r="P32" s="28" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q32" s="28" t="s">
         <v>234</v>
@@ -34951,13 +34913,11 @@
         <v>235</v>
       </c>
       <c r="S32" s="36" t="s">
-        <v>245</v>
-      </c>
-      <c r="T32" s="37" t="s">
+        <v>243</v>
+      </c>
+      <c r="T32" s="37"/>
+      <c r="U32" s="35" t="s">
         <v>236</v>
-      </c>
-      <c r="U32" s="35" t="s">
-        <v>237</v>
       </c>
       <c r="V32" s="42" t="s">
         <v>182</v>
@@ -34969,7 +34929,7 @@
         <v>187</v>
       </c>
       <c r="Y32" s="35" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="Z32" s="1">
         <v>0.5</v>
@@ -34980,7 +34940,7 @@
       </c>
       <c r="AB32" s="1">
         <f t="shared" si="6"/>
-        <v>0.6875</v>
+        <v>0.625</v>
       </c>
       <c r="AD32" s="43">
         <f t="shared" si="7"/>
@@ -34994,15 +34954,15 @@
       </c>
       <c r="B33">
         <f t="shared" si="2"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C33">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D33">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E33" s="13" t="s">
         <v>53</v>
@@ -35035,19 +34995,17 @@
         <v>235</v>
       </c>
       <c r="S33" s="36" t="s">
-        <v>245</v>
-      </c>
-      <c r="T33" s="37" t="s">
+        <v>243</v>
+      </c>
+      <c r="T33" s="37"/>
+      <c r="U33" s="35" t="s">
         <v>236</v>
       </c>
-      <c r="U33" s="35" t="s">
+      <c r="V33" s="42">
+        <v>1</v>
+      </c>
+      <c r="W33" s="42" t="s">
         <v>237</v>
-      </c>
-      <c r="V33" s="42">
-        <v>1</v>
-      </c>
-      <c r="W33" s="42" t="s">
-        <v>238</v>
       </c>
       <c r="X33" s="42">
         <v>1</v>
@@ -35064,7 +35022,7 @@
       </c>
       <c r="AB33" s="1">
         <f t="shared" si="6"/>
-        <v>0.75</v>
+        <v>0.6875</v>
       </c>
       <c r="AD33" s="43">
         <f t="shared" si="7"/>
@@ -35078,15 +35036,15 @@
       </c>
       <c r="B34">
         <f t="shared" si="2"/>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C34">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D34">
         <f t="shared" si="4"/>
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E34" s="13" t="s">
         <v>74</v>
@@ -35110,21 +35068,17 @@
       <c r="N34" s="41"/>
       <c r="O34" s="41"/>
       <c r="P34" s="41" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q34" s="41"/>
       <c r="R34" s="41" t="s">
         <v>235</v>
       </c>
       <c r="S34" s="36"/>
-      <c r="T34" s="37" t="s">
-        <v>236</v>
-      </c>
-      <c r="U34" s="35" t="s">
-        <v>244</v>
-      </c>
+      <c r="T34" s="37"/>
+      <c r="U34" s="35"/>
       <c r="V34" s="42" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="W34" s="42" t="s">
         <v>182</v>
@@ -35133,22 +35087,22 @@
         <v>163</v>
       </c>
       <c r="Y34" s="35" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="Z34" s="1">
         <v>0.4375</v>
       </c>
       <c r="AA34">
         <f t="shared" si="5"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB34" s="1">
         <f t="shared" si="6"/>
-        <v>0.5</v>
+        <v>0.375</v>
       </c>
       <c r="AD34" s="43">
         <f t="shared" si="7"/>
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35" spans="1:30" x14ac:dyDescent="0.3">
@@ -35158,11 +35112,11 @@
       </c>
       <c r="B35">
         <f t="shared" si="2"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C35">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D35">
         <f t="shared" si="4"/>
@@ -35188,7 +35142,7 @@
       <c r="L35" s="41"/>
       <c r="M35" s="41"/>
       <c r="N35" s="41" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="O35" s="41" t="s">
         <v>233</v>
@@ -35199,19 +35153,17 @@
         <v>235</v>
       </c>
       <c r="S35" s="36" t="s">
-        <v>245</v>
-      </c>
-      <c r="T35" s="37" t="s">
+        <v>243</v>
+      </c>
+      <c r="T35" s="37"/>
+      <c r="U35" s="35" t="s">
         <v>236</v>
       </c>
-      <c r="U35" s="35" t="s">
+      <c r="V35" s="42">
+        <v>1</v>
+      </c>
+      <c r="W35" s="42" t="s">
         <v>237</v>
-      </c>
-      <c r="V35" s="42">
-        <v>1</v>
-      </c>
-      <c r="W35" s="42" t="s">
-        <v>238</v>
       </c>
       <c r="X35" s="42" t="s">
         <v>163</v>
@@ -35228,7 +35180,7 @@
       </c>
       <c r="AB35" s="1">
         <f t="shared" si="6"/>
-        <v>0.6875</v>
+        <v>0.625</v>
       </c>
       <c r="AD35" s="43">
         <f t="shared" si="7"/>
@@ -35242,15 +35194,15 @@
       </c>
       <c r="B36">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C36">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D36">
         <f t="shared" si="4"/>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E36" s="13" t="s">
         <v>67</v>
@@ -35281,16 +35233,14 @@
         <v>235</v>
       </c>
       <c r="S36" s="36" t="s">
-        <v>245</v>
-      </c>
-      <c r="T36" s="37" t="s">
+        <v>243</v>
+      </c>
+      <c r="T36" s="37"/>
+      <c r="U36" s="35" t="s">
         <v>236</v>
       </c>
-      <c r="U36" s="35" t="s">
-        <v>237</v>
-      </c>
       <c r="V36" s="42" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="W36" s="42" t="s">
         <v>182</v>
@@ -35310,7 +35260,7 @@
       </c>
       <c r="AB36" s="1">
         <f t="shared" si="6"/>
-        <v>0.625</v>
+        <v>0.5625</v>
       </c>
       <c r="AD36" s="43">
         <f t="shared" si="7"/>
@@ -35324,15 +35274,15 @@
       </c>
       <c r="B37">
         <f t="shared" si="2"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C37">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D37">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E37" s="13" t="s">
         <v>76</v>
@@ -35358,7 +35308,7 @@
         <v>233</v>
       </c>
       <c r="P37" s="28" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q37" s="28" t="s">
         <v>234</v>
@@ -35367,16 +35317,14 @@
         <v>235</v>
       </c>
       <c r="S37" s="36" t="s">
-        <v>245</v>
-      </c>
-      <c r="T37" s="37" t="s">
+        <v>243</v>
+      </c>
+      <c r="T37" s="37"/>
+      <c r="U37" s="35" t="s">
         <v>236</v>
       </c>
-      <c r="U37" s="35" t="s">
+      <c r="V37" s="42" t="s">
         <v>237</v>
-      </c>
-      <c r="V37" s="42" t="s">
-        <v>238</v>
       </c>
       <c r="W37" s="42">
         <v>1</v>
@@ -35385,7 +35333,7 @@
         <v>182</v>
       </c>
       <c r="Y37" s="35" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="Z37" s="1">
         <v>0.6875</v>
@@ -35396,7 +35344,7 @@
       </c>
       <c r="AB37" s="1">
         <f t="shared" si="6"/>
-        <v>0.75</v>
+        <v>0.6875</v>
       </c>
       <c r="AD37" s="43">
         <f t="shared" si="7"/>
@@ -35410,15 +35358,15 @@
       </c>
       <c r="B38">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C38">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D38">
         <f t="shared" si="4"/>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E38" s="13" t="s">
         <v>79</v>
@@ -35440,11 +35388,11 @@
       <c r="L38" s="28"/>
       <c r="M38" s="28"/>
       <c r="N38" s="28" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="O38" s="28"/>
       <c r="P38" s="28" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q38" s="28" t="s">
         <v>234</v>
@@ -35453,23 +35401,21 @@
         <v>235</v>
       </c>
       <c r="S38" s="36"/>
-      <c r="T38" s="37" t="s">
+      <c r="T38" s="37"/>
+      <c r="U38" s="35" t="s">
         <v>236</v>
-      </c>
-      <c r="U38" s="35" t="s">
-        <v>237</v>
       </c>
       <c r="V38" s="42" t="s">
         <v>182</v>
       </c>
       <c r="W38" s="42" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="X38" s="42" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="Y38" s="35" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="Z38" s="1">
         <v>0.5</v>
@@ -35480,7 +35426,7 @@
       </c>
       <c r="AB38" s="1">
         <f t="shared" si="6"/>
-        <v>0.625</v>
+        <v>0.5625</v>
       </c>
       <c r="AD38" s="43">
         <f t="shared" si="7"/>
@@ -35488,13 +35434,13 @@
       </c>
     </row>
     <row r="39" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A39" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+      <c r="A39" s="2">
+        <f t="shared" si="1"/>
+        <v>75.5</v>
       </c>
       <c r="B39">
         <f t="shared" si="2"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C39">
         <f t="shared" si="3"/>
@@ -35502,7 +35448,7 @@
       </c>
       <c r="D39">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E39" s="13" t="s">
         <v>81</v>
@@ -35522,7 +35468,7 @@
         <v>232</v>
       </c>
       <c r="L39" s="38" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="M39" s="38"/>
       <c r="N39" s="38"/>
@@ -35530,7 +35476,7 @@
         <v>233</v>
       </c>
       <c r="P39" s="38" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q39" s="38" t="s">
         <v>234</v>
@@ -35539,13 +35485,13 @@
         <v>235</v>
       </c>
       <c r="S39" s="36" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="T39" s="37" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="U39" s="36" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="V39" s="42">
         <v>1</v>
@@ -35553,8 +35499,8 @@
       <c r="W39" s="42" t="s">
         <v>182</v>
       </c>
-      <c r="X39" s="42" t="s">
-        <v>177</v>
+      <c r="X39" s="42">
+        <v>1</v>
       </c>
       <c r="Y39" s="36" t="s">
         <v>184</v>
@@ -35564,15 +35510,15 @@
       </c>
       <c r="AA39">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB39" s="1">
         <f t="shared" si="6"/>
-        <v>0.8125</v>
+        <v>0.875</v>
       </c>
       <c r="AD39" s="43">
         <f t="shared" si="7"/>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:30" x14ac:dyDescent="0.3">
@@ -35582,11 +35528,11 @@
       </c>
       <c r="B40">
         <f t="shared" si="2"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C40">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D40">
         <f t="shared" si="4"/>
@@ -35610,25 +35556,23 @@
       <c r="L40" s="37"/>
       <c r="M40" s="37"/>
       <c r="N40" s="37" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="O40" s="37"/>
       <c r="P40" s="37" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q40" s="37"/>
       <c r="R40" s="37" t="s">
         <v>235</v>
       </c>
       <c r="S40" s="36"/>
-      <c r="T40" s="37" t="s">
+      <c r="T40" s="37"/>
+      <c r="U40" s="35" t="s">
         <v>236</v>
       </c>
-      <c r="U40" s="35" t="s">
+      <c r="V40" s="42" t="s">
         <v>237</v>
-      </c>
-      <c r="V40" s="42" t="s">
-        <v>238</v>
       </c>
       <c r="W40" s="42" t="s">
         <v>157</v>
@@ -35637,7 +35581,7 @@
         <v>182</v>
       </c>
       <c r="Y40" s="35" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="Z40" s="1">
         <v>0.5</v>
@@ -35648,7 +35592,7 @@
       </c>
       <c r="AB40" s="1">
         <f t="shared" si="6"/>
-        <v>0.5</v>
+        <v>0.4375</v>
       </c>
       <c r="AD40" s="43">
         <f t="shared" si="7"/>
@@ -35670,7 +35614,7 @@
       </c>
       <c r="D41">
         <f t="shared" si="4"/>
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E41" s="13" t="s">
         <v>54</v>
@@ -35700,10 +35644,10 @@
       </c>
       <c r="S41" s="36"/>
       <c r="T41" s="37" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="U41" s="36" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="V41" s="42" t="s">
         <v>182</v>
@@ -35712,17 +35656,17 @@
         <v>1</v>
       </c>
       <c r="X41" s="42" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="Y41" s="36" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="Z41" s="1">
         <v>0.5</v>
       </c>
       <c r="AA41">
         <f t="shared" si="5"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB41" s="1">
         <f t="shared" si="6"/>
@@ -35730,7 +35674,7 @@
       </c>
       <c r="AD41" s="43">
         <f t="shared" si="7"/>
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42" spans="1:30" x14ac:dyDescent="0.3">
@@ -35740,11 +35684,11 @@
       </c>
       <c r="B42">
         <f t="shared" si="2"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C42">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D42">
         <f t="shared" si="4"/>
@@ -35772,20 +35716,18 @@
       <c r="N42" s="37"/>
       <c r="O42" s="37"/>
       <c r="P42" s="37" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q42" s="37"/>
       <c r="R42" s="37" t="s">
         <v>235</v>
       </c>
       <c r="S42" s="36" t="s">
-        <v>245</v>
-      </c>
-      <c r="T42" s="37" t="s">
+        <v>243</v>
+      </c>
+      <c r="T42" s="37"/>
+      <c r="U42" s="36" t="s">
         <v>236</v>
-      </c>
-      <c r="U42" s="36" t="s">
-        <v>237</v>
       </c>
       <c r="V42" s="42">
         <v>1</v>
@@ -35808,7 +35750,7 @@
       </c>
       <c r="AB42" s="1">
         <f t="shared" si="6"/>
-        <v>0.6875</v>
+        <v>0.625</v>
       </c>
       <c r="AD42" s="43">
         <f t="shared" si="7"/>
@@ -35822,15 +35764,15 @@
       </c>
       <c r="B43">
         <f t="shared" si="2"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C43">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D43">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E43" s="13" t="s">
         <v>73</v>
@@ -35852,7 +35794,7 @@
       <c r="L43" s="37"/>
       <c r="M43" s="37"/>
       <c r="N43" s="37" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="O43" s="37" t="s">
         <v>233</v>
@@ -35865,13 +35807,11 @@
         <v>235</v>
       </c>
       <c r="S43" s="36" t="s">
-        <v>245</v>
-      </c>
-      <c r="T43" s="37" t="s">
+        <v>243</v>
+      </c>
+      <c r="T43" s="37"/>
+      <c r="U43" s="36" t="s">
         <v>236</v>
-      </c>
-      <c r="U43" s="36" t="s">
-        <v>237</v>
       </c>
       <c r="V43" s="42">
         <v>1</v>
@@ -35883,7 +35823,7 @@
         <v>163</v>
       </c>
       <c r="Y43" s="36" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="Z43" s="1">
         <v>0.6875</v>
@@ -35894,7 +35834,7 @@
       </c>
       <c r="AB43" s="1">
         <f t="shared" si="6"/>
-        <v>0.75</v>
+        <v>0.6875</v>
       </c>
       <c r="AD43" s="43">
         <f t="shared" si="7"/>
@@ -35908,11 +35848,11 @@
       </c>
       <c r="B44">
         <f t="shared" si="2"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C44">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D44">
         <f t="shared" si="4"/>
@@ -35940,7 +35880,7 @@
       <c r="N44" s="37"/>
       <c r="O44" s="37"/>
       <c r="P44" s="37" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q44" s="37" t="s">
         <v>234</v>
@@ -35949,14 +35889,12 @@
         <v>235</v>
       </c>
       <c r="S44" s="36" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="T44" s="37" t="s">
-        <v>243</v>
-      </c>
-      <c r="U44" s="36" t="s">
-        <v>244</v>
-      </c>
+        <v>242</v>
+      </c>
+      <c r="U44" s="36"/>
       <c r="V44" s="42">
         <v>1</v>
       </c>
@@ -35964,10 +35902,10 @@
         <v>163</v>
       </c>
       <c r="X44" s="42" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="Y44" s="36" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="Z44" s="1">
         <v>0.5</v>
@@ -35978,7 +35916,7 @@
       </c>
       <c r="AB44" s="1">
         <f t="shared" si="6"/>
-        <v>0.6875</v>
+        <v>0.625</v>
       </c>
       <c r="AD44" s="43">
         <f t="shared" si="7"/>
@@ -35991,13 +35929,13 @@
       <c r="X45" s="42"/>
       <c r="AD45" s="10">
         <f>COUNTIF(AD10:AD44,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46" spans="1:30" x14ac:dyDescent="0.3">
       <c r="AD46" s="43">
         <f>SUM(AD10:AD44)/AD45</f>
-        <v>150</v>
+        <v>75.5</v>
       </c>
     </row>
   </sheetData>
@@ -36055,15 +35993,29 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:AD46"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" style="39" customWidth="1"/>
     <col min="2" max="4" width="8" style="39" customWidth="1"/>
-    <col min="5" max="5" width="22" style="39" customWidth="1"/>
-    <col min="6" max="18" width="17.6640625" style="39" customWidth="1"/>
-    <col min="19" max="19" width="23.5546875" style="39" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="17.6640625" style="39" customWidth="1"/>
+    <col min="5" max="5" width="18.88671875" style="39" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.21875" style="39" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="26.88671875" style="39" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.6640625" style="39" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.44140625" style="39" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.5546875" style="39" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15" style="39" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.33203125" style="39" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.44140625" style="39" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.21875" style="39" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.5546875" style="39" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17.77734375" style="39" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.109375" style="39" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.109375" style="39" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.77734375" style="39" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="22.6640625" style="39" customWidth="1"/>
+    <col min="21" max="21" width="16" style="39" bestFit="1" customWidth="1"/>
     <col min="22" max="25" width="17" style="39" customWidth="1"/>
     <col min="26" max="27" width="12" style="39" customWidth="1"/>
     <col min="28" max="28" width="10" style="39" customWidth="1"/>
@@ -36073,7 +36025,7 @@
   <sheetData>
     <row r="1" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A1" s="54" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B1" s="45"/>
       <c r="C1" s="45"/>
@@ -36135,22 +36087,54 @@
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
       <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="5"/>
-      <c r="M4" s="5"/>
-      <c r="N4" s="5"/>
-      <c r="O4" s="5"/>
-      <c r="P4" s="5"/>
-      <c r="Q4" s="5"/>
-      <c r="R4" s="5"/>
-      <c r="S4" s="5"/>
-      <c r="T4" s="5"/>
-      <c r="U4" s="5"/>
+      <c r="F4" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="L4" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="M4" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="N4" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="O4" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="P4" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q4" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="R4" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="S4" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="T4" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="U4" s="5" t="s">
+        <v>113</v>
+      </c>
       <c r="V4" s="5"/>
       <c r="W4" s="5"/>
       <c r="X4" s="5"/>
@@ -36164,22 +36148,54 @@
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
-      <c r="N5" s="5"/>
-      <c r="O5" s="5"/>
-      <c r="P5" s="5"/>
-      <c r="Q5" s="5"/>
-      <c r="R5" s="5"/>
-      <c r="S5" s="5"/>
-      <c r="T5" s="5"/>
-      <c r="U5" s="5"/>
+      <c r="F5" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="M5" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="O5" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="P5" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q5" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="R5" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="S5" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="T5" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="U5" s="5" t="s">
+        <v>101</v>
+      </c>
       <c r="V5" s="5"/>
       <c r="W5" s="5"/>
       <c r="X5" s="5"/>
@@ -36223,67 +36239,67 @@
       <c r="D7" s="8"/>
       <c r="E7" s="8"/>
       <c r="F7" s="8">
-        <f t="shared" ref="F7:U7" si="0">IFERROR(COUNTIF(F10:F44, F$4)/COUNTA(B10:B44),0)</f>
+        <f>IFERROR(COUNTIF(F10:F44, G$4)/COUNTA(B10:B44),0)</f>
         <v>0</v>
       </c>
       <c r="G7" s="8">
-        <f t="shared" si="0"/>
+        <f>IFERROR(COUNTIF(G10:G44, H$4)/COUNTA(C10:C44),0)</f>
         <v>0</v>
       </c>
       <c r="H7" s="8">
-        <f t="shared" si="0"/>
+        <f>IFERROR(COUNTIF(H10:H44, I$4)/COUNTA(D10:D44),0)</f>
         <v>0</v>
       </c>
       <c r="I7" s="8">
-        <f t="shared" si="0"/>
+        <f>IFERROR(COUNTIF(I10:I44, J$4)/COUNTA(E10:E44),0)</f>
         <v>0</v>
       </c>
       <c r="J7" s="8">
-        <f t="shared" si="0"/>
+        <f>IFERROR(COUNTIF(J10:J44, K$4)/COUNTA(F10:F44),0)</f>
         <v>0</v>
       </c>
       <c r="K7" s="8">
-        <f t="shared" si="0"/>
+        <f>IFERROR(COUNTIF(K10:K44, L$4)/COUNTA(G10:G44),0)</f>
         <v>0</v>
       </c>
       <c r="L7" s="8">
-        <f t="shared" si="0"/>
+        <f>IFERROR(COUNTIF(L10:L44, M$4)/COUNTA(H10:H44),0)</f>
         <v>0</v>
       </c>
       <c r="M7" s="8">
-        <f t="shared" si="0"/>
+        <f>IFERROR(COUNTIF(M10:M44, N$4)/COUNTA(I10:I44),0)</f>
         <v>0</v>
       </c>
       <c r="N7" s="8">
-        <f t="shared" si="0"/>
+        <f>IFERROR(COUNTIF(N10:N44, O$4)/COUNTA(J10:J44),0)</f>
         <v>0</v>
       </c>
       <c r="O7" s="8">
-        <f t="shared" si="0"/>
+        <f>IFERROR(COUNTIF(O10:O44, P$4)/COUNTA(K10:K44),0)</f>
         <v>0</v>
       </c>
       <c r="P7" s="8">
-        <f t="shared" si="0"/>
+        <f>IFERROR(COUNTIF(P10:P44, Q$4)/COUNTA(L10:L44),0)</f>
         <v>0</v>
       </c>
       <c r="Q7" s="8">
-        <f t="shared" si="0"/>
+        <f>IFERROR(COUNTIF(Q10:Q44, R$4)/COUNTA(M10:M44),0)</f>
         <v>0</v>
       </c>
       <c r="R7" s="8">
-        <f t="shared" si="0"/>
+        <f>IFERROR(COUNTIF(R10:R44, S$4)/COUNTA(N10:N44),0)</f>
         <v>0</v>
       </c>
       <c r="S7" s="8">
-        <f t="shared" si="0"/>
+        <f>IFERROR(COUNTIF(S10:S44, T$4)/COUNTA(O10:O44),0)</f>
         <v>0</v>
       </c>
       <c r="T7" s="8">
-        <f t="shared" si="0"/>
+        <f>IFERROR(COUNTIF(T10:T44, U$4)/COUNTA(P10:P44),0)</f>
         <v>0</v>
       </c>
       <c r="U7" s="8">
-        <f t="shared" si="0"/>
+        <f>IFERROR( COUNTIF(U10:U44,#REF!)/COUNTA(Q10:Q44),0)</f>
         <v>0</v>
       </c>
       <c r="V7" s="7"/>
@@ -36291,6 +36307,26 @@
       <c r="X7" s="7"/>
       <c r="Y7" s="7"/>
     </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="F8" s="39" t="s">
+        <v>250</v>
+      </c>
+      <c r="G8" s="39" t="s">
+        <v>255</v>
+      </c>
+      <c r="I8" s="39" t="s">
+        <v>251</v>
+      </c>
+      <c r="K8" s="39" t="s">
+        <v>252</v>
+      </c>
+      <c r="N8" s="39" t="s">
+        <v>253</v>
+      </c>
+      <c r="P8" s="39" t="s">
+        <v>254</v>
+      </c>
+    </row>
     <row r="9" spans="1:30" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
         <v>228</v>
@@ -36382,1261 +36418,1261 @@
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
-        <f t="shared" ref="A10:A44" si="1">_xlfn.IFNA(IF(AD10=0,$AD$46,""),"")</f>
+        <f t="shared" ref="A10:A44" si="0">_xlfn.IFNA(IF(AD10=0,$AD$46,""),"")</f>
         <v>0</v>
       </c>
       <c r="B10">
-        <f t="shared" ref="B10:B44" si="2">SUM(V10:X10)+C10</f>
+        <f t="shared" ref="B10:B44" si="1">SUM(V10:X10)+C10</f>
         <v>0</v>
       </c>
       <c r="C10">
-        <f t="shared" ref="C10:C44" si="3">COUNTA(F10:U10)</f>
+        <f t="shared" ref="C10:C44" si="2">COUNTA(F10:U10)</f>
         <v>0</v>
       </c>
       <c r="D10">
-        <f t="shared" ref="D10:D44" si="4">_xlfn.RANK.EQ(B10,$B$10:$B$44,0)</f>
+        <f t="shared" ref="D10:D44" si="3">_xlfn.RANK.EQ(B10,$B$10:$B$44,0)</f>
         <v>1</v>
       </c>
       <c r="V10" s="11"/>
       <c r="Y10" s="11"/>
       <c r="Z10" s="1">
-        <f t="shared" ref="Z10:Z44" si="5">IFERROR(COUNTIF(F10:U10,"W")/COUNTA(F10:U10),0)</f>
+        <f t="shared" ref="Z10:Z44" si="4">IFERROR(COUNTIF(F10:U10,"W")/COUNTA(F10:U10),0)</f>
         <v>0</v>
       </c>
       <c r="AA10">
-        <f t="shared" ref="AA10:AA44" si="6">MAX($B$10:$B$44)-B10</f>
+        <f t="shared" ref="AA10:AA44" si="5">MAX($B$10:$B$44)-B10</f>
         <v>0</v>
       </c>
       <c r="AB10" s="1">
-        <f t="shared" ref="AB10:AB44" si="7">IFERROR(B10/16,0)</f>
+        <f t="shared" ref="AB10:AB44" si="6">IFERROR(B10/16,0)</f>
         <v>0</v>
       </c>
       <c r="AD10" s="43">
-        <f t="shared" ref="AD10:AD44" si="8">MAX($B$7:$B$141)-B10</f>
+        <f t="shared" ref="AD10:AD44" si="7">MAX($B$7:$B$141)-B10</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="B11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="V11" s="12"/>
       <c r="Y11" s="12"/>
       <c r="Z11" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AA11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AB11" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AD11" s="43">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="B12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="V12" s="12"/>
       <c r="Y12" s="12"/>
       <c r="Z12" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AA12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AB12" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AD12" s="43">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="B13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="V13" s="12"/>
       <c r="Y13" s="12"/>
       <c r="Z13" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AA13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AB13" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AD13" s="43">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="B14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="V14" s="12"/>
       <c r="Y14" s="12"/>
       <c r="Z14" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AA14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AB14" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AD14" s="43">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="B15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="V15" s="12"/>
       <c r="Y15" s="12"/>
       <c r="Z15" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AA15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AB15" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AD15" s="43">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="B16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="V16" s="12"/>
       <c r="Y16" s="12"/>
       <c r="Z16" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AA16">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AB16" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AD16" s="43">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="B17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="V17" s="12"/>
       <c r="Y17" s="12"/>
       <c r="Z17" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AA17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AB17" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AD17" s="43">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="B18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="V18" s="12"/>
       <c r="Y18" s="12"/>
       <c r="Z18" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AA18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AB18" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AD18" s="43">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="B19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="V19" s="12"/>
       <c r="Y19" s="12"/>
       <c r="Z19" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AA19">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AB19" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AD19" s="43">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="B20">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D20">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="V20" s="12"/>
       <c r="Y20" s="12"/>
       <c r="Z20" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AA20">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AB20" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AD20" s="43">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="B21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D21">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="V21" s="12"/>
       <c r="Y21" s="12"/>
       <c r="Z21" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AA21">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AB21" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AD21" s="43">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="B22">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C22">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D22">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="V22" s="12"/>
       <c r="Y22" s="12"/>
       <c r="Z22" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AA22">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AB22" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AD22" s="43">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="B23">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C23">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D23">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="V23" s="12"/>
       <c r="Y23" s="12"/>
       <c r="Z23" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AA23">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AB23" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AD23" s="43">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="B24">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C24">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D24">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="V24" s="12"/>
       <c r="Y24" s="12"/>
       <c r="Z24" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AA24">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AB24" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AD24" s="43">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="B25">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C25">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D25">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="V25" s="12"/>
       <c r="Y25" s="12"/>
       <c r="Z25" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AA25">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AB25" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AD25" s="43">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="B26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C26">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D26">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="V26" s="12"/>
       <c r="Y26" s="12"/>
       <c r="Z26" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AA26">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AB26" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AD26" s="43">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="B27">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D27">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="V27" s="12"/>
       <c r="Y27" s="12"/>
       <c r="Z27" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AA27">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AB27" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AD27" s="43">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="B28">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C28">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D28">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="V28" s="12"/>
       <c r="Y28" s="12"/>
       <c r="Z28" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AA28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AB28" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AD28" s="43">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="B29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C29">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D29">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="V29" s="12"/>
       <c r="Y29" s="12"/>
       <c r="Z29" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AA29">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AB29" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AD29" s="43">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="B30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D30">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="V30" s="12"/>
       <c r="Y30" s="12"/>
       <c r="Z30" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AA30">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AB30" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AD30" s="43">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="B31">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D31">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="V31" s="12"/>
       <c r="Y31" s="12"/>
       <c r="Z31" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AA31">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AB31" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AD31" s="43">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="B32">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C32">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D32">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="V32" s="12"/>
       <c r="Y32" s="12"/>
       <c r="Z32" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AA32">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AB32" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AD32" s="43">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="B33">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C33">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D33">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="V33" s="12"/>
       <c r="Y33" s="12"/>
       <c r="Z33" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AA33">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AB33" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AD33" s="43">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="B34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C34">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="V34" s="12"/>
       <c r="Y34" s="12"/>
       <c r="Z34" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AA34">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AB34" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AD34" s="43">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="B35">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C35">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D35">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="V35" s="12"/>
       <c r="Y35" s="12"/>
       <c r="Z35" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AA35">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AB35" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AD35" s="43">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="B36">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C36">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D36">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="V36" s="12"/>
       <c r="Y36" s="12"/>
       <c r="Z36" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AA36">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AB36" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AD36" s="43">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="B37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D37">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="V37" s="12"/>
       <c r="Y37" s="12"/>
       <c r="Z37" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AA37">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AB37" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AD37" s="43">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="B38">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C38">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D38">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="V38" s="12"/>
       <c r="Y38" s="12"/>
       <c r="Z38" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AA38">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AB38" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AD38" s="43">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="B39">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C39">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="V39" s="12"/>
       <c r="Y39" s="12"/>
       <c r="Z39" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AA39">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AB39" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AD39" s="43">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="B40">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C40">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D40">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="V40" s="12"/>
       <c r="Y40" s="12"/>
       <c r="Z40" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AA40">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AB40" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AD40" s="43">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="B41">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C41">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D41">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="V41" s="12"/>
       <c r="Y41" s="12"/>
       <c r="Z41" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AA41">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AB41" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AD41" s="43">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="B42">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C42">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D42">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="V42" s="12"/>
       <c r="Y42" s="12"/>
       <c r="Z42" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AA42">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AB42" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AD42" s="43">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="B43">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C43">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D43">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="V43" s="12"/>
       <c r="Y43" s="12"/>
       <c r="Z43" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AA43">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AB43" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AD43" s="43">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A44" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="B44">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C44">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D44">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="V44" s="12"/>
       <c r="Y44" s="12"/>
       <c r="Z44" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AA44">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AB44" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AD44" s="43">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -37725,7 +37761,7 @@
   <sheetData>
     <row r="1" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A1" s="54" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B1" s="45"/>
       <c r="C1" s="45"/>
@@ -39377,7 +39413,7 @@
   <sheetData>
     <row r="1" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A1" s="54" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B1" s="45"/>
       <c r="C1" s="45"/>
@@ -41029,7 +41065,7 @@
   <sheetData>
     <row r="1" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A1" s="54" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B1" s="45"/>
       <c r="C1" s="45"/>
